--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,165 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUCHINCLOSS, JAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRICKLAND, MARILYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THANEDAR, SHRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -69,45 +228,6 @@
     <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
     <x:t>HILL, JAMES FRENCH</x:t>
   </x:si>
   <x:si>
@@ -123,9 +243,6 @@
     <x:t>PATRONIS, JIMMY JR.</x:t>
   </x:si>
   <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
     <x:t>FINE, RANDY</x:t>
   </x:si>
   <x:si>
@@ -135,27 +252,18 @@
     <x:t>GAINES, HOUSTON</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>SMITH, ADRIAN</x:t>
   </x:si>
   <x:si>
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
     <x:t>BONCK, JON</x:t>
   </x:si>
   <x:si>
     <x:t>38</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
   </x:si>
   <x:si>
@@ -180,9 +288,6 @@
     <x:t>NEHLS, TREVER</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
     <x:t>DE LA CRUZ, CARLOS JR.</x:t>
   </x:si>
   <x:si>
@@ -192,57 +297,21 @@
     <x:t>BAIRD, JAMES R DR.</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
     <x:t>IN</x:t>
   </x:si>
   <x:si>
     <x:t>TIMMONS, WILLIAM R IV</x:t>
   </x:si>
   <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
     <x:t>ROUNDS, MIKE</x:t>
   </x:si>
   <x:si>
     <x:t>SD</x:t>
   </x:si>
   <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
     <x:t>SCOTT, DAVID ALBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
     <x:t>BUDZINSKI, NIKKI</x:t>
   </x:si>
   <x:si>
@@ -361,75 +430,6 @@
   </x:si>
   <x:si>
     <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUCHINCLOSS, JAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRICKLAND, MARILYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANEDAR, SHRI</x:t>
   </x:si>
   <x:si>
     <x:t>GOODLANDER, MAGGIE</x:t>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -968,10 +968,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>2479136</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -985,16 +985,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>10015605</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,804 +1002,804 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>455146</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>7170138</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>400022</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>418058</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>558813</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>1673736</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>430866</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F13" s="1">
-        <x:v>708828</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>282975</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>348433</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>771658</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>461942</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91656</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>426281</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>141263</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>615886</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>513868</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>487316</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>411748</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>12254527</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>735613</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>1419040</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B28" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>56045</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>83860</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>262965</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>111599</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>109274</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>487174</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>106348</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>107940</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>172296</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>98455</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>516368</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>47162</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,229 +1807,229 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>382680</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>377124</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>380377</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>107387</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>4239904</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>557012</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>5259858</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>6471279</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1012792</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>20483</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>119844</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,729 +2060,729 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>285009</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>30220</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>91847</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>300000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>550000</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>350000</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>350000</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>628597</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>221403</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>250000</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>350000</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>350000</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="B63" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B63" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C63" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>300000</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="C64" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>500000</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>547042</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>455146</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>300000</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>7170138</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>189528</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>511996</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>300000</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>400022</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D73" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="E73" s="1" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D73" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E73" s="1" t="s">
-        <x:v>130</x:v>
-      </x:c>
       <x:c r="F73" s="1">
-        <x:v>113120</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>103020</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>508142</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>151713</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>430866</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>1762153</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F79" s="1">
         <x:v>34890</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F80" s="1">
         <x:v>418060</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F81" s="1">
         <x:v>80948</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
         <x:v>137</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
         <x:v>138</x:v>
@@ -2791,297 +2791,297 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F83" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F84" s="1">
         <x:v>708827</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
         <x:v>139</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F85" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F86" s="1">
         <x:v>282975</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F87" s="1">
         <x:v>348433</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F88" s="1">
         <x:v>771658</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F89" s="1">
         <x:v>461943</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F90" s="1">
         <x:v>91656</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F91" s="1">
         <x:v>426280</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F92" s="1">
         <x:v>141263</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F93" s="1">
         <x:v>616386</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F94" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>142</x:v>
@@ -3090,412 +3090,412 @@
         <x:v>157560</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="F96" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F97" s="1">
         <x:v>487317</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F98" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F99" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F100" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B101" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D101" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E101" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B101" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="C101" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D101" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E101" s="1" t="s">
-        <x:v>64</x:v>
       </x:c>
       <x:c r="F101" s="1">
         <x:v>12203100</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F102" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F103" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F104" s="1">
         <x:v>628597</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F105" s="1">
         <x:v>221403</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F106" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F107" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F108" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>735613</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F110" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F111" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="F112" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
         <x:v>146</x:v>
@@ -3504,7 +3504,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3553,70 +3553,70 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -3624,7 +3624,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>142</x:v>
@@ -3633,670 +3633,670 @@
         <x:v>157560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>19</x:v>
-      </x:c>
-      <x:c r="B25" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
@@ -4304,84 +4304,84 @@
         <x:v>139</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
@@ -4389,7 +4389,7 @@
         <x:v>137</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
         <x:v>138</x:v>
@@ -4398,296 +4398,296 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5">
@@ -4695,67 +4695,67 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5">
@@ -4763,16 +4763,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5">
@@ -4780,33 +4780,33 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5">
@@ -4814,7 +4814,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>146</x:v>
@@ -4823,7 +4823,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4868,63 +4868,63 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>142</x:v>
@@ -4933,544 +4933,544 @@
         <x:v>157560</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
         <x:v>138</x:v>
@@ -5479,348 +5479,348 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
         <x:v>146</x:v>
@@ -5829,7 +5829,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5870,35 +5870,35 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -5909,172 +5909,172 @@
         <x:v>157560</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
@@ -6085,128 +6085,128 @@
         <x:v>150000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -6217,7 +6217,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,7 +6550,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>142</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,7 +6781,7 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
         <x:v>138</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,7 +6968,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>146</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,12 +42,231 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00915181</x:t>
   </x:si>
   <x:si>
     <x:t>FELLOWSHIP PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>GOODLANDER, MAGGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, DONAVAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STANTON, GREG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
     <x:t>TORRES, RITCHIE JOHN</x:t>
   </x:si>
   <x:si>
@@ -57,36 +276,129 @@
     <x:t>NY</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
   </x:si>
   <x:si>
     <x:t>GRAHAM, LINDSEY O.</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
     <x:t>COLLINS, MICHAEL A JR</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>MORRIS, NATE</x:t>
   </x:si>
   <x:si>
@@ -102,81 +414,27 @@
     <x:t>RICKETTS, PETE</x:t>
   </x:si>
   <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
     <x:t>PAXTON, WARREN KENNETH JR.</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
     <x:t>CARL, JERRY LEE, JR</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUCHINCLOSS, JAKE</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
     <x:t>MA</x:t>
   </x:si>
   <x:si>
     <x:t>HUIZENGA, WILLIAM P</x:t>
   </x:si>
   <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
     <x:t>DELBENE, SUZAN K</x:t>
   </x:si>
   <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
     <x:t>STRICKLAND, MARILYN</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>BEGICH, NICHOLAS III</x:t>
   </x:si>
   <x:si>
@@ -186,268 +444,10 @@
     <x:t>FRANKEL, LOIS J.</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
     <x:t>KINGSTON, JACK REP.</x:t>
   </x:si>
   <x:si>
     <x:t>THANEDAR, SHRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODLANDER, MAGGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, DONAVAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STANTON, GREG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZ</x:t>
   </x:si>
   <x:si>
     <x:t>SCHRIER, KIM DR.</x:t>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>300000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -956,22 +956,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>550000</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -979,22 +979,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,22 +1002,22 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>350000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -1025,22 +1025,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>628597</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -1048,22 +1048,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>221403</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1077,39 +1077,39 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>250000</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -1117,22 +1117,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>350000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1140,22 +1140,22 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>300000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1163,22 +1163,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>500000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1186,22 +1186,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>547042</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1209,22 +1209,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>455146</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1232,22 +1232,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>300000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1255,22 +1255,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>7170138</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1278,22 +1278,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>189528</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1301,22 +1301,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>511996</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1324,22 +1324,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>300000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1347,91 +1347,91 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F20" s="1">
+        <x:v>817066</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F20" s="1">
-        <x:v>400022</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>113120</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>103020</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>508142</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1439,22 +1439,22 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>151713</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1462,22 +1462,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>430866</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1485,22 +1485,22 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>1762153</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1508,91 +1508,91 @@
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>817066</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2479136</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>10015605</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>455146</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1600,22 +1600,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>7170138</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1623,22 +1623,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>400022</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1646,22 +1646,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>418058</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1669,22 +1669,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>80948</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1692,22 +1692,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>558813</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1715,22 +1715,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>1673736</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1738,22 +1738,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>430866</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1761,22 +1761,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>708828</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>12</x:v>
@@ -1784,22 +1784,22 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>282975</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,22 +1807,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>348433</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1830,22 +1830,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>771658</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1853,22 +1853,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>461942</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1876,22 +1876,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>91656</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1899,22 +1899,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>426281</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1922,22 +1922,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>141263</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1945,45 +1945,45 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C46" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D46" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F46" s="1">
+        <x:v>56045</x:v>
+      </x:c>
+      <x:c r="G46" s="1" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="C46" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D46" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F46" s="1">
-        <x:v>615886</x:v>
-      </x:c>
-      <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>513868</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1991,22 +1991,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>487316</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -2014,22 +2014,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>411748</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>12254527</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,22 +2060,22 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>735613</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2083,22 +2083,22 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>1419040</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -2106,45 +2106,45 @@
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>56045</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>83860</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2152,22 +2152,22 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>262965</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2175,22 +2175,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E56" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="D56" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="E56" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="F56" s="1">
-        <x:v>111599</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2198,45 +2198,45 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>109274</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>487174</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>12</x:v>
@@ -2244,22 +2244,22 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>106348</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2267,22 +2267,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>107940</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2290,22 +2290,22 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>172296</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2313,22 +2313,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>98455</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2336,22 +2336,22 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>516368</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2359,45 +2359,45 @@
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>47162</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B65" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C65" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D65" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="E65" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="B65" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C65" s="1" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D65" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="E65" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="F65" s="1">
-        <x:v>382680</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2405,22 +2405,22 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>377124</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2428,68 +2428,68 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>380377</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>107387</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>4239904</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>12</x:v>
@@ -2497,22 +2497,22 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>557012</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -2520,22 +2520,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>5259858</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
@@ -2543,22 +2543,22 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>6471279</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,22 +2566,22 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>1012792</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>12</x:v>
@@ -2589,68 +2589,68 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>20483</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>119844</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>285009</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2658,22 +2658,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>30220</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2681,22 +2681,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>91847</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2704,22 +2704,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>34890</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2727,22 +2727,22 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>418060</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2750,22 +2750,22 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>80948</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>12</x:v>
@@ -2773,22 +2773,22 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>150000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>12</x:v>
@@ -2796,22 +2796,22 @@
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>430866</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>12</x:v>
@@ -2819,22 +2819,22 @@
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>708827</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>12</x:v>
@@ -2842,45 +2842,45 @@
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>268690</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>282975</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
         <x:v>12</x:v>
@@ -2888,22 +2888,22 @@
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>348433</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>12</x:v>
@@ -2911,22 +2911,22 @@
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B88" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C88" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D88" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E88" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B88" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C88" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D88" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="E88" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F88" s="1">
-        <x:v>771658</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
         <x:v>12</x:v>
@@ -2934,22 +2934,22 @@
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D89" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="D89" s="1" t="s">
+      <x:c r="E89" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="E89" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="F89" s="1">
-        <x:v>461943</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
         <x:v>12</x:v>
@@ -2957,22 +2957,22 @@
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>91656</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
         <x:v>12</x:v>
@@ -2980,22 +2980,22 @@
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>426280</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
         <x:v>12</x:v>
@@ -3003,22 +3003,22 @@
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>141263</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
         <x:v>12</x:v>
@@ -3026,22 +3026,22 @@
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>616386</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
         <x:v>12</x:v>
@@ -3049,22 +3049,22 @@
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>506917</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
         <x:v>12</x:v>
@@ -3072,22 +3072,22 @@
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>157560</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
         <x:v>12</x:v>
@@ -3095,22 +3095,22 @@
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B96" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C96" s="1" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="D96" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E96" s="1" t="s">
         <x:v>32</x:v>
       </x:c>
-      <x:c r="B96" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C96" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D96" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E96" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="F96" s="1">
-        <x:v>513868</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
         <x:v>12</x:v>
@@ -3118,19 +3118,19 @@
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F97" s="1">
         <x:v>487317</x:v>
@@ -3141,19 +3141,19 @@
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F98" s="1">
         <x:v>105040</x:v>
@@ -3164,19 +3164,19 @@
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F99" s="1">
         <x:v>550000</x:v>
@@ -3187,19 +3187,19 @@
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F100" s="1">
         <x:v>411748</x:v>
@@ -3210,19 +3210,19 @@
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F101" s="1">
         <x:v>12203100</x:v>
@@ -3233,19 +3233,19 @@
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F102" s="1">
         <x:v>350000</x:v>
@@ -3256,19 +3256,19 @@
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F103" s="1">
         <x:v>350000</x:v>
@@ -3279,19 +3279,19 @@
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F104" s="1">
         <x:v>628597</x:v>
@@ -3302,19 +3302,19 @@
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F105" s="1">
         <x:v>221403</x:v>
@@ -3325,19 +3325,19 @@
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F106" s="1">
         <x:v>250000</x:v>
@@ -3348,19 +3348,19 @@
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F107" s="1">
         <x:v>350000</x:v>
@@ -3371,19 +3371,19 @@
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F108" s="1">
         <x:v>350000</x:v>
@@ -3394,19 +3394,19 @@
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>735613</x:v>
@@ -3417,19 +3417,19 @@
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="F110" s="1">
         <x:v>300000</x:v>
@@ -3440,19 +3440,19 @@
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F111" s="1">
         <x:v>2250000</x:v>
@@ -3463,19 +3463,19 @@
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="F112" s="1">
         <x:v>150000</x:v>
@@ -3486,16 +3486,16 @@
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
         <x:v>146</x:v>
@@ -3553,13 +3553,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
@@ -3570,13 +3570,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
@@ -3587,13 +3587,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
@@ -3604,13 +3604,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
@@ -3621,13 +3621,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
@@ -3638,13 +3638,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
@@ -3655,13 +3655,13 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
@@ -3672,13 +3672,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
@@ -3689,13 +3689,13 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
@@ -3706,13 +3706,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
@@ -3723,13 +3723,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
@@ -3740,13 +3740,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
@@ -3757,13 +3757,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
@@ -3774,13 +3774,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
@@ -3791,13 +3791,13 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
@@ -3808,13 +3808,13 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
@@ -3825,13 +3825,13 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
@@ -3842,13 +3842,13 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
@@ -3859,13 +3859,13 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
@@ -3876,13 +3876,13 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
@@ -3893,13 +3893,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
@@ -3910,30 +3910,30 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
@@ -3944,13 +3944,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
@@ -3961,13 +3961,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
@@ -3978,13 +3978,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
@@ -3995,64 +3995,64 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
@@ -4063,13 +4063,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
@@ -4080,13 +4080,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
@@ -4097,13 +4097,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
@@ -4114,13 +4114,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
@@ -4131,13 +4131,13 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
@@ -4148,13 +4148,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
@@ -4165,13 +4165,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
@@ -4182,13 +4182,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
@@ -4199,13 +4199,13 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
@@ -4216,13 +4216,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
@@ -4233,13 +4233,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
@@ -4250,13 +4250,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
@@ -4267,13 +4267,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
@@ -4284,13 +4284,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
@@ -4301,30 +4301,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
@@ -4335,13 +4335,13 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
@@ -4352,13 +4352,13 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
@@ -4369,13 +4369,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
@@ -4386,13 +4386,13 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
@@ -4403,13 +4403,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
@@ -4420,13 +4420,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
@@ -4437,13 +4437,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
@@ -4454,13 +4454,13 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
@@ -4471,13 +4471,13 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
@@ -4488,13 +4488,13 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
@@ -4505,13 +4505,13 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
@@ -4522,13 +4522,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
@@ -4539,13 +4539,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
@@ -4556,13 +4556,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
@@ -4573,30 +4573,30 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
@@ -4607,13 +4607,13 @@
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
@@ -4624,13 +4624,13 @@
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
@@ -4641,13 +4641,13 @@
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
@@ -4658,13 +4658,13 @@
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
@@ -4675,13 +4675,13 @@
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
@@ -4695,10 +4695,10 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
@@ -4709,30 +4709,30 @@
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
@@ -4743,13 +4743,13 @@
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
@@ -4760,13 +4760,13 @@
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
@@ -4780,10 +4780,10 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
@@ -4794,13 +4794,13 @@
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
@@ -4814,7 +4814,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>146</x:v>
@@ -4868,10 +4868,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -4882,10 +4882,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
@@ -4896,10 +4896,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
@@ -4910,10 +4910,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -4924,10 +4924,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -4938,10 +4938,10 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
@@ -4952,10 +4952,10 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
@@ -4966,10 +4966,10 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
@@ -4980,10 +4980,10 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
@@ -4994,10 +4994,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
@@ -5008,10 +5008,10 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
@@ -5022,10 +5022,10 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
@@ -5036,10 +5036,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
@@ -5050,10 +5050,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
@@ -5064,10 +5064,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
@@ -5078,10 +5078,10 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
@@ -5092,10 +5092,10 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
@@ -5106,10 +5106,10 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
@@ -5120,10 +5120,10 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
@@ -5134,10 +5134,10 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
@@ -5148,24 +5148,24 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
@@ -5176,10 +5176,10 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
@@ -5190,10 +5190,10 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
@@ -5204,52 +5204,52 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
@@ -5260,10 +5260,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
@@ -5274,10 +5274,10 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
@@ -5288,10 +5288,10 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
@@ -5302,10 +5302,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
@@ -5316,10 +5316,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
@@ -5330,10 +5330,10 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
@@ -5344,10 +5344,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
@@ -5358,10 +5358,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
@@ -5372,10 +5372,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
@@ -5386,10 +5386,10 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
@@ -5400,24 +5400,24 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
@@ -5428,10 +5428,10 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
@@ -5442,10 +5442,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
@@ -5456,10 +5456,10 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
@@ -5470,10 +5470,10 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
@@ -5484,10 +5484,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
@@ -5498,10 +5498,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
@@ -5512,10 +5512,10 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
@@ -5526,10 +5526,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
@@ -5540,10 +5540,10 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
@@ -5554,10 +5554,10 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
@@ -5568,10 +5568,10 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
@@ -5582,10 +5582,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
@@ -5596,10 +5596,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
@@ -5610,10 +5610,10 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
@@ -5624,24 +5624,24 @@
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
@@ -5652,10 +5652,10 @@
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
@@ -5666,10 +5666,10 @@
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
@@ -5680,10 +5680,10 @@
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
@@ -5694,10 +5694,10 @@
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
@@ -5708,10 +5708,10 @@
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
@@ -5722,10 +5722,10 @@
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
@@ -5736,24 +5736,24 @@
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
@@ -5764,10 +5764,10 @@
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
@@ -5778,10 +5778,10 @@
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
@@ -5792,10 +5792,10 @@
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
@@ -5806,10 +5806,10 @@
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
@@ -5820,7 +5820,7 @@
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
         <x:v>146</x:v>
@@ -5870,7 +5870,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -5881,7 +5881,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -5892,7 +5892,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -5903,7 +5903,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -5914,7 +5914,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -5925,7 +5925,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -5936,18 +5936,18 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
@@ -5958,18 +5958,18 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
@@ -5980,7 +5980,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
@@ -5991,7 +5991,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
@@ -6002,7 +6002,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
@@ -6013,7 +6013,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
@@ -6024,7 +6024,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
@@ -6035,18 +6035,18 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
@@ -6057,7 +6057,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
@@ -6068,7 +6068,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
@@ -6079,7 +6079,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
@@ -6090,7 +6090,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
@@ -6101,7 +6101,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
@@ -6112,7 +6112,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
@@ -6123,7 +6123,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
@@ -6134,7 +6134,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
@@ -6145,18 +6145,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
@@ -6167,7 +6167,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
@@ -6178,18 +6178,18 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
@@ -6200,7 +6200,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,10 +6550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,7 +6968,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>146</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,46 +42,328 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
     <x:t>PROTECT PROGRESS</x:t>
   </x:si>
   <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
     <x:t>MENENDEZ, ROBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
   </x:si>
   <x:si>
     <x:t>C00915181</x:t>
@@ -90,364 +372,82 @@
     <x:t>FELLOWSHIP PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUCHINCLOSS, JAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRICKLAND, MARILYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THANEDAR, SHRI</x:t>
+  </x:si>
+  <x:si>
     <x:t>GOODLANDER, MAGGIE</x:t>
   </x:si>
   <x:si>
     <x:t>NH</x:t>
   </x:si>
   <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCKINNEY, DONAVAN</x:t>
   </x:si>
   <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCKINNEY, AMANDA</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
     <x:t>STANTON, GREG</x:t>
   </x:si>
   <x:si>
     <x:t>AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUCHINCLOSS, JAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRICKLAND, MARILYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANEDAR, SHRI</x:t>
   </x:si>
   <x:si>
     <x:t>SCHRIER, KIM DR.</x:t>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>34890</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -956,22 +956,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>418060</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -979,22 +979,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>80948</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,551 +1002,551 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>150000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>430866</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>708827</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F8" s="1">
-        <x:v>268690</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>282975</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>348433</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>771658</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>461943</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>91656</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>426280</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>141263</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>616386</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>506917</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>157560</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>513868</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>817066</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>2479136</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="F22" s="1">
-        <x:v>10015605</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>455146</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>7170138</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>400022</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>418058</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>80948</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>558813</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1554,252 +1554,252 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>1673736</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>430866</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>708828</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>282975</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>348433</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>771658</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>461942</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>91656</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>426281</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>141263</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>615886</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,229 +1807,229 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>513868</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>487316</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>411748</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>12254527</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>735613</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>1419040</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>56045</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>83860</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>262965</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>111599</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>109274</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,804 +2060,804 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>487174</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>106348</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>107940</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>172296</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>98455</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>516368</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>47162</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>382680</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>377124</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>380377</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>107387</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>4239904</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>557012</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>5259858</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>6471279</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>1012792</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>20483</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>119844</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>285009</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>30220</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>91847</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>300000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>550000</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>350000</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>350000</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>628597</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B77" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C77" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E77" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B77" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C77" s="1" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D77" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E77" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F77" s="1">
-        <x:v>221403</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>250000</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>350000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>350000</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>300000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>500000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>547042</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>455146</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>300000</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>12</x:v>
@@ -2865,637 +2865,637 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>7170138</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>189528</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>511996</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>300000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>400022</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>113120</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>103020</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>508142</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>151713</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>430866</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>1762153</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F97" s="1">
         <x:v>487317</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F98" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F99" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F100" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E101" s="1" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="E101" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="F101" s="1">
         <x:v>12203100</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E102" s="1" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="E102" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="F102" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B103" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C103" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D103" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E103" s="1" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="B103" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C103" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D103" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E103" s="1" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="F103" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F104" s="1">
         <x:v>628597</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F105" s="1">
         <x:v>221403</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F106" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F107" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F108" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>735613</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F110" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F111" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F112" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
         <x:v>146</x:v>
@@ -3504,7 +3504,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3553,1141 +3553,1141 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="B64" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C64" s="1" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5">
@@ -4695,84 +4695,84 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5">
@@ -4780,33 +4780,33 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5">
@@ -4814,7 +4814,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>146</x:v>
@@ -4823,7 +4823,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4868,959 +4868,959 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="B3" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
         <x:v>146</x:v>
@@ -5829,7 +5829,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5870,343 +5870,343 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -6217,7 +6217,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,10 +6550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,7 +6968,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>146</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,129 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STANTON, GREG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCHRIER, KIM DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WARNER, MARK ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -69,36 +192,15 @@
     <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
     <x:t>06</x:t>
   </x:si>
   <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOORE, BLAKE</x:t>
   </x:si>
   <x:si>
@@ -144,24 +246,15 @@
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
     <x:t>BONCK, JON</x:t>
   </x:si>
   <x:si>
     <x:t>38</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
     <x:t>MEALER, ALEXANDRA</x:t>
   </x:si>
   <x:si>
@@ -189,45 +282,6 @@
     <x:t>35</x:t>
   </x:si>
   <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TORRES, RITCHIE JOHN</x:t>
   </x:si>
   <x:si>
@@ -339,9 +393,6 @@
     <x:t>11</x:t>
   </x:si>
   <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
     <x:t>PEKARSKY, STELLA</x:t>
   </x:si>
   <x:si>
@@ -366,36 +417,6 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
     <x:t>CARL, JERRY LEE, JR</x:t>
   </x:si>
   <x:si>
@@ -411,9 +432,6 @@
     <x:t>DELBENE, SUZAN K</x:t>
   </x:si>
   <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
     <x:t>STRICKLAND, MARILYN</x:t>
   </x:si>
   <x:si>
@@ -442,24 +460,6 @@
   </x:si>
   <x:si>
     <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STANTON, GREG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCHRIER, KIM DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WARNER, MARK ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAGEMAN, HARRIET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -956,22 +956,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>2479136</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -979,22 +979,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>10015605</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,10 +1002,10 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>19</x:v>
@@ -1017,536 +1017,536 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>455146</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>7170138</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>400022</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
       <x:c r="F8" s="1">
-        <x:v>418058</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>558813</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>1673736</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>430866</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>708828</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>348433</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>771658</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>461942</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91656</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>426281</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>141263</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>615886</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>513868</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>487316</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>411748</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>12254527</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>735613</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>1419040</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>56045</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1554,252 +1554,252 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
+      <x:c r="D29" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F29" s="1">
-        <x:v>83860</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D30" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="F30" s="1">
-        <x:v>262965</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>111599</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>109274</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>487174</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>106348</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>107940</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>172296</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>98455</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>516368</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>47162</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,229 +1807,229 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>382680</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>377124</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>380377</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>107387</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>4239904</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>557012</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E46" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="E46" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="F46" s="1">
-        <x:v>5259858</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>6471279</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1012792</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>20483</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>119844</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,804 +2060,804 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>285009</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>30220</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>91847</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>300000</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>550000</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>350000</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>350000</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>628597</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>221403</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>250000</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C61" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B61" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C61" s="1" t="s">
-        <x:v>122</x:v>
-      </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>350000</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="C62" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>350000</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>300000</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>500000</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>547042</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>455146</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>300000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>7170138</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>189528</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>511996</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>300000</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>400022</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>113120</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>103020</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>508142</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>151713</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>430866</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>1762153</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>34890</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>418060</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>150000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>430866</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>708827</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>268690</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>12</x:v>
@@ -2865,646 +2865,646 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>282975</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>348433</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>771658</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>461943</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>91656</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>426280</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>141263</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>616386</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>506917</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C95" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="D95" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="E95" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C95" s="1" t="s">
-        <x:v>141</x:v>
-      </x:c>
-      <x:c r="D95" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E95" s="1" t="s">
-        <x:v>142</x:v>
-      </x:c>
       <x:c r="F95" s="1">
-        <x:v>157560</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>513868</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>487317</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>105040</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>550000</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>411748</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>12203100</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>350000</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>628597</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>221403</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>250000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>350000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>350000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>735613</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>300000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>2250000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>150000</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>515838</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3553,1277 +3553,1277 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>97</x:v>
-      </x:c>
-      <x:c r="B13" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C13" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="C50" s="1" t="s">
         <x:v>39</x:v>
-      </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="C50" s="1" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="C67" s="1" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5">
       <x:c r="A69" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5">
       <x:c r="A74" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5">
       <x:c r="A76" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4868,968 +4868,968 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B61" s="1" t="s">
         <x:v>43</x:v>
-      </x:c>
-      <x:c r="B61" s="1" t="s">
-        <x:v>44</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C70" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5870,354 +5870,354 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6462,7 +6462,7 @@
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>515838</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,10 +6550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
         <x:v>18</x:v>
-      </x:c>
-      <x:c r="B33" s="1" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,10 +6968,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>515838</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -48,418 +48,418 @@
     <x:t>PROTECT PROGRESS</x:t>
   </x:si>
   <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODLANDER, MAGGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, DONAVAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUCHINCLOSS, JAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRICKLAND, MARILYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THANEDAR, SHRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
     <x:t>STANTON, GREG</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
     <x:t>AZ</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
     <x:t>SCHRIER, KIM DR.</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>WARNER, MARK ROBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
     <x:t>HAGEMAN, HARRIET</x:t>
   </x:si>
   <x:si>
     <x:t>WY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUCHINCLOSS, JAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRICKLAND, MARILYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANEDAR, SHRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODLANDER, MAGGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, DONAVAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>157560</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -965,13 +965,13 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>513868</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -985,16 +985,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>487317</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,22 +1002,22 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>105040</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -1025,22 +1025,22 @@
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>550000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -1054,16 +1054,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>411748</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1071,45 +1071,45 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>12203100</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -1117,22 +1117,22 @@
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>350000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1140,22 +1140,22 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>628597</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1163,22 +1163,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>221403</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1186,22 +1186,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>250000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1209,22 +1209,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>350000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1232,22 +1232,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1261,16 +1261,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>735613</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1278,71 +1278,71 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>300000</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>2250000</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>150000</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
@@ -1353,16 +1353,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>515838</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1370,71 +1370,71 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>817066</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>2479136</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>10015605</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
@@ -1445,16 +1445,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>455146</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1468,16 +1468,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>7170138</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1491,16 +1491,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>400022</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
         <x:v>12</x:v>
@@ -1514,16 +1514,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>418058</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
         <x:v>12</x:v>
@@ -1537,16 +1537,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>80948</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1560,16 +1560,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>558813</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1583,16 +1583,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>1673736</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1606,16 +1606,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>430866</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1629,16 +1629,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>708828</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1652,16 +1652,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>282975</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1675,16 +1675,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>348433</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1698,16 +1698,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>771658</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1721,16 +1721,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>461942</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1744,16 +1744,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>91656</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1767,16 +1767,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>426281</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>12</x:v>
@@ -1790,16 +1790,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>141263</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1813,16 +1813,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>615886</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1836,16 +1836,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>513868</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1853,22 +1853,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>487316</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1876,45 +1876,45 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>411748</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>12254527</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1922,22 +1922,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>735613</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1951,16 +1951,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>1419040</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1974,19 +1974,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>56045</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
@@ -1997,16 +1997,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>83860</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -2020,16 +2020,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>262965</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2043,16 +2043,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>111599</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2066,16 +2066,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>109274</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2089,16 +2089,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>487174</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
         <x:v>12</x:v>
@@ -2112,16 +2112,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>106348</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2135,19 +2135,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>107940</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
@@ -2158,16 +2158,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>172296</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2181,16 +2181,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>98455</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2204,16 +2204,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>516368</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2227,19 +2227,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>47162</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
@@ -2250,16 +2250,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>382680</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2273,16 +2273,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>377124</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2296,16 +2296,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>380377</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2319,16 +2319,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>107387</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2342,16 +2342,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>4239904</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
         <x:v>12</x:v>
@@ -2365,19 +2365,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>557012</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
@@ -2388,19 +2388,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>5259858</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
@@ -2411,16 +2411,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>6471279</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2434,16 +2434,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>1012792</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2451,68 +2451,68 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>20483</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>119844</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>285009</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -2520,22 +2520,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>30220</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
@@ -2543,22 +2543,22 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>91847</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,22 +2566,22 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B73" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B73" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>300000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
         <x:v>12</x:v>
@@ -2589,22 +2589,22 @@
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B74" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B74" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>550000</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
         <x:v>12</x:v>
@@ -2612,22 +2612,22 @@
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B75" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B75" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2635,19 +2635,19 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B76" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B76" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F76" s="1">
         <x:v>350000</x:v>
@@ -2658,22 +2658,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B77" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B77" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>628597</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2681,22 +2681,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B78" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B78" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>221403</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2704,22 +2704,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B79" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B79" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>250000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2727,22 +2727,22 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>350000</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2750,22 +2750,22 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>350000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>12</x:v>
@@ -2773,19 +2773,19 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B82" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B82" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F82" s="1">
         <x:v>300000</x:v>
@@ -2796,22 +2796,22 @@
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>500000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>12</x:v>
@@ -2819,22 +2819,22 @@
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>547042</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>12</x:v>
@@ -2848,16 +2848,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>455146</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>12</x:v>
@@ -2865,19 +2865,19 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B86" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B86" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F86" s="1">
         <x:v>300000</x:v>
@@ -2894,16 +2894,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>7170138</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>12</x:v>
@@ -2917,16 +2917,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D88" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="E88" s="1" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="D88" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E88" s="1" t="s">
-        <x:v>134</x:v>
-      </x:c>
       <x:c r="F88" s="1">
-        <x:v>189528</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
         <x:v>12</x:v>
@@ -2934,22 +2934,22 @@
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>511996</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
         <x:v>12</x:v>
@@ -2957,22 +2957,22 @@
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>300000</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
         <x:v>12</x:v>
@@ -2980,22 +2980,22 @@
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>400022</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
         <x:v>12</x:v>
@@ -3003,22 +3003,22 @@
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>113120</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
         <x:v>12</x:v>
@@ -3032,16 +3032,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>103020</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
         <x:v>12</x:v>
@@ -3055,16 +3055,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>508142</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
         <x:v>12</x:v>
@@ -3078,16 +3078,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>151713</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
         <x:v>12</x:v>
@@ -3101,16 +3101,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>430866</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
         <x:v>12</x:v>
@@ -3118,22 +3118,22 @@
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>1762153</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
         <x:v>12</x:v>
@@ -3147,16 +3147,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>34890</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
         <x:v>12</x:v>
@@ -3164,22 +3164,22 @@
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>418060</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
         <x:v>12</x:v>
@@ -3193,16 +3193,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>80948</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
         <x:v>12</x:v>
@@ -3210,22 +3210,22 @@
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>150000</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
         <x:v>12</x:v>
@@ -3233,22 +3233,22 @@
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
         <x:v>12</x:v>
@@ -3256,22 +3256,22 @@
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>708827</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
         <x:v>12</x:v>
@@ -3279,45 +3279,45 @@
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>268690</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>282975</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
         <x:v>12</x:v>
@@ -3325,22 +3325,22 @@
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>348433</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
         <x:v>12</x:v>
@@ -3348,22 +3348,22 @@
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>771658</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
         <x:v>12</x:v>
@@ -3371,22 +3371,22 @@
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>461943</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
         <x:v>12</x:v>
@@ -3400,16 +3400,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>91656</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
         <x:v>12</x:v>
@@ -3417,22 +3417,22 @@
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>426280</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
         <x:v>12</x:v>
@@ -3440,22 +3440,22 @@
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>141263</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
         <x:v>12</x:v>
@@ -3463,22 +3463,22 @@
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>616386</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
         <x:v>12</x:v>
@@ -3492,16 +3492,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="D113" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E113" s="1" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="D113" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="E113" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F113" s="1">
-        <x:v>506917</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
         <x:v>12</x:v>
@@ -3553,13 +3553,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
@@ -3570,13 +3570,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
@@ -3587,13 +3587,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
@@ -3604,13 +3604,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
@@ -3621,13 +3621,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
@@ -3638,13 +3638,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
@@ -3655,13 +3655,13 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
@@ -3672,13 +3672,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
@@ -3689,13 +3689,13 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
@@ -3706,13 +3706,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
@@ -3723,13 +3723,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
@@ -3740,13 +3740,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
@@ -3757,13 +3757,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
@@ -3774,13 +3774,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
@@ -3791,13 +3791,13 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
@@ -3808,13 +3808,13 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
@@ -3825,13 +3825,13 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
@@ -3842,13 +3842,13 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
@@ -3859,13 +3859,13 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
@@ -3876,13 +3876,13 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
@@ -3893,13 +3893,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
@@ -3910,30 +3910,30 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
@@ -3944,13 +3944,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
@@ -3961,13 +3961,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
@@ -3978,13 +3978,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
@@ -3998,33 +3998,33 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
@@ -4035,24 +4035,24 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
@@ -4063,13 +4063,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
@@ -4080,13 +4080,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
@@ -4097,13 +4097,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
@@ -4114,13 +4114,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
@@ -4131,13 +4131,13 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
@@ -4148,13 +4148,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
@@ -4165,13 +4165,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
@@ -4182,13 +4182,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
@@ -4199,13 +4199,13 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
@@ -4216,13 +4216,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
@@ -4233,13 +4233,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
@@ -4250,13 +4250,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
@@ -4267,13 +4267,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
@@ -4284,13 +4284,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
@@ -4301,30 +4301,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
@@ -4335,13 +4335,13 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
@@ -4352,13 +4352,13 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
@@ -4369,13 +4369,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
@@ -4386,13 +4386,13 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
@@ -4403,13 +4403,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
@@ -4420,13 +4420,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
@@ -4437,13 +4437,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
@@ -4454,13 +4454,13 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
@@ -4471,13 +4471,13 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
@@ -4488,13 +4488,13 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
@@ -4505,13 +4505,13 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
@@ -4522,13 +4522,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
@@ -4539,13 +4539,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
@@ -4556,13 +4556,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
@@ -4573,30 +4573,30 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
@@ -4607,13 +4607,13 @@
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
@@ -4624,13 +4624,13 @@
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
@@ -4641,13 +4641,13 @@
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
@@ -4658,13 +4658,13 @@
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
@@ -4675,13 +4675,13 @@
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
@@ -4692,13 +4692,13 @@
     </x:row>
     <x:row r="69" spans="1:5">
       <x:c r="A69" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
@@ -4709,30 +4709,30 @@
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
@@ -4743,13 +4743,13 @@
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
@@ -4760,13 +4760,13 @@
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
@@ -4777,13 +4777,13 @@
     </x:row>
     <x:row r="74" spans="1:5">
       <x:c r="A74" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
@@ -4794,13 +4794,13 @@
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
@@ -4811,13 +4811,13 @@
     </x:row>
     <x:row r="76" spans="1:5">
       <x:c r="A76" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>515838</x:v>
@@ -4868,10 +4868,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -4882,10 +4882,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
@@ -4896,10 +4896,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
@@ -4910,10 +4910,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -4924,10 +4924,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -4938,10 +4938,10 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
@@ -4952,10 +4952,10 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
@@ -4966,10 +4966,10 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
@@ -4980,10 +4980,10 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
@@ -4994,10 +4994,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
@@ -5008,10 +5008,10 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
@@ -5022,10 +5022,10 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
@@ -5036,10 +5036,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
@@ -5050,10 +5050,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
@@ -5064,10 +5064,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
@@ -5078,10 +5078,10 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
@@ -5092,10 +5092,10 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
@@ -5106,10 +5106,10 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
@@ -5120,10 +5120,10 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
@@ -5134,10 +5134,10 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
@@ -5148,24 +5148,24 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
@@ -5176,10 +5176,10 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
@@ -5190,10 +5190,10 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
@@ -5204,30 +5204,30 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
@@ -5235,21 +5235,21 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
@@ -5260,10 +5260,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
@@ -5274,10 +5274,10 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
@@ -5288,10 +5288,10 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
@@ -5302,10 +5302,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
@@ -5316,10 +5316,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
@@ -5330,10 +5330,10 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
@@ -5344,10 +5344,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
@@ -5358,10 +5358,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
@@ -5372,10 +5372,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
@@ -5386,10 +5386,10 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
@@ -5400,24 +5400,24 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
@@ -5428,10 +5428,10 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
@@ -5442,10 +5442,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
@@ -5456,10 +5456,10 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
@@ -5470,10 +5470,10 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
@@ -5484,10 +5484,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
@@ -5498,10 +5498,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
@@ -5512,10 +5512,10 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
@@ -5526,10 +5526,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
@@ -5540,10 +5540,10 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
@@ -5554,10 +5554,10 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
@@ -5568,10 +5568,10 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
@@ -5582,10 +5582,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
@@ -5596,10 +5596,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
@@ -5610,10 +5610,10 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
@@ -5624,24 +5624,24 @@
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
@@ -5652,10 +5652,10 @@
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
@@ -5666,10 +5666,10 @@
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
@@ -5680,10 +5680,10 @@
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
@@ -5694,10 +5694,10 @@
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
@@ -5708,10 +5708,10 @@
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
@@ -5722,10 +5722,10 @@
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
@@ -5736,24 +5736,24 @@
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
@@ -5764,10 +5764,10 @@
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
@@ -5778,10 +5778,10 @@
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
@@ -5792,10 +5792,10 @@
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
@@ -5806,10 +5806,10 @@
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
@@ -5820,10 +5820,10 @@
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C70" s="1">
         <x:v>515838</x:v>
@@ -5870,7 +5870,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -5881,7 +5881,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -5892,7 +5892,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -5903,7 +5903,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -5914,7 +5914,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -5925,7 +5925,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -5936,18 +5936,18 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
@@ -5958,18 +5958,18 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
@@ -5980,7 +5980,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
@@ -5991,7 +5991,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
@@ -6002,7 +6002,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
@@ -6013,7 +6013,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
@@ -6024,7 +6024,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
@@ -6035,18 +6035,18 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
@@ -6057,7 +6057,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
@@ -6068,7 +6068,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
@@ -6079,7 +6079,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
@@ -6090,7 +6090,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
@@ -6101,7 +6101,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
@@ -6112,7 +6112,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
@@ -6123,7 +6123,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
@@ -6134,7 +6134,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
@@ -6145,18 +6145,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
@@ -6167,7 +6167,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
@@ -6178,18 +6178,18 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
@@ -6200,7 +6200,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
@@ -6211,7 +6211,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>515838</x:v>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6462,7 +6462,7 @@
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>515838</x:v>
@@ -6509,7 +6509,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6520,7 +6520,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6542,7 +6542,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6553,7 +6553,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6564,7 +6564,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6575,7 +6575,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6586,7 +6586,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6597,7 +6597,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6619,7 +6619,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6641,7 +6641,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6652,7 +6652,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6663,7 +6663,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6696,7 +6696,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6707,7 +6707,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6718,7 +6718,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6740,7 +6740,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6751,7 +6751,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6762,7 +6762,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6795,7 +6795,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6817,7 +6817,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6828,7 +6828,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6850,7 +6850,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6872,7 +6872,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6883,7 +6883,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6905,7 +6905,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6916,7 +6916,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6938,7 +6938,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6949,7 +6949,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6960,7 +6960,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6971,7 +6971,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>515838</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,46 +42,328 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00848440</x:t>
   </x:si>
   <x:si>
     <x:t>PROTECT PROGRESS</x:t>
   </x:si>
   <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
     <x:t>MENENDEZ, ROBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
   </x:si>
   <x:si>
     <x:t>C00915181</x:t>
@@ -90,355 +372,73 @@
     <x:t>FELLOWSHIP PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUCHINCLOSS, JAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRICKLAND, MARILYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THANEDAR, SHRI</x:t>
+  </x:si>
+  <x:si>
     <x:t>GOODLANDER, MAGGIE</x:t>
   </x:si>
   <x:si>
     <x:t>NH</x:t>
   </x:si>
   <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>MCKINNEY, DONAVAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUCHINCLOSS, JAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRICKLAND, MARILYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANEDAR, SHRI</x:t>
   </x:si>
   <x:si>
     <x:t>MCKINNEY, AMANDA</x:t>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>34890</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -956,22 +956,22 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B3" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B3" s="1" t="s">
+      <x:c r="D3" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D3" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>418060</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -979,22 +979,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>80948</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,551 +1002,551 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="E5" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
       <x:c r="F5" s="1">
-        <x:v>150000</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>430866</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E7" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E7" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
       <x:c r="F7" s="1">
-        <x:v>708827</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F8" s="1">
-        <x:v>268690</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>282975</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>348433</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>771658</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>461943</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>91656</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>426280</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>141263</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>616386</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>817066</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>2479136</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>10015605</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>455146</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>7170138</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>400022</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>418058</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>80948</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="F25" s="1">
-        <x:v>558813</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="F26" s="1">
-        <x:v>1673736</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>430866</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>708828</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1554,252 +1554,252 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>282975</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>348433</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>771658</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>461942</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>91656</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>426281</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>141263</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>615886</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>513868</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>487316</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>411748</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,229 +1807,229 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>12254527</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>735613</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E42" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="E42" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
       <x:c r="F42" s="1">
-        <x:v>1419040</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>56045</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>83860</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>262965</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>111599</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>109274</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>487174</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>106348</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>107940</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,804 +2060,804 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>172296</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>98455</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>516368</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>47162</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>382680</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>377124</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>380377</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>107387</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>4239904</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>557012</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>5259858</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>6471279</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>1012792</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>20483</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>119844</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>285009</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>30220</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>91847</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>300000</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>550000</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>350000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>628597</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>221403</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>250000</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>350000</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B77" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C77" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="D77" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="E77" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B77" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C77" s="1" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="D77" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E77" s="1" t="s">
-        <x:v>36</x:v>
-      </x:c>
       <x:c r="F77" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>300000</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>500000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>547042</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>455146</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>300000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>7170138</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>189528</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>511996</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>12</x:v>
@@ -2865,223 +2865,223 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>300000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>400022</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>113120</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>103020</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>508142</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>151713</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>430866</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>1762153</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
         <x:v>140</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F94" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
         <x:v>141</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
         <x:v>142</x:v>
@@ -3090,412 +3090,412 @@
         <x:v>157560</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F96" s="1">
         <x:v>513868</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F97" s="1">
         <x:v>487317</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
         <x:v>143</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F98" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F99" s="1">
         <x:v>550000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F100" s="1">
         <x:v>411748</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F101" s="1">
         <x:v>12203100</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F102" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B103" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C103" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D103" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E103" s="1" t="s">
         <x:v>21</x:v>
-      </x:c>
-      <x:c r="B103" s="1" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C103" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D103" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="E103" s="1" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="F103" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F104" s="1">
         <x:v>628597</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F105" s="1">
         <x:v>221403</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F106" s="1">
         <x:v>250000</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F107" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F108" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F109" s="1">
         <x:v>735613</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F110" s="1">
         <x:v>300000</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F111" s="1">
         <x:v>2250000</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
         <x:v>144</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F112" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
         <x:v>145</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
         <x:v>146</x:v>
@@ -3504,7 +3504,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3553,70 +3553,70 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
@@ -3624,7 +3624,7 @@
         <x:v>141</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>142</x:v>
@@ -3633,1061 +3633,1061 @@
         <x:v>157560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B64" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C64" s="1" t="s">
         <x:v>44</x:v>
-      </x:c>
-      <x:c r="B64" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C64" s="1" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5">
@@ -4695,67 +4695,67 @@
         <x:v>144</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5">
@@ -4763,16 +4763,16 @@
         <x:v>140</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5">
@@ -4780,33 +4780,33 @@
         <x:v>143</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5">
@@ -4814,7 +4814,7 @@
         <x:v>145</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
         <x:v>146</x:v>
@@ -4823,7 +4823,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4868,63 +4868,63 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>142</x:v>
@@ -4933,894 +4933,894 @@
         <x:v>157560</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
         <x:v>146</x:v>
@@ -5829,7 +5829,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5870,35 +5870,35 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
@@ -5909,304 +5909,304 @@
         <x:v>157560</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
@@ -6217,7 +6217,7 @@
         <x:v>515838</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,7 +6550,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
         <x:v>142</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,7 +6968,7 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
         <x:v>146</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,138 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STANTON, GREG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCHRIER, KIM DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WARNER, MARK ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -69,36 +201,15 @@
     <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
     <x:t>06</x:t>
   </x:si>
   <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOORE, BLAKE</x:t>
   </x:si>
   <x:si>
@@ -144,24 +255,15 @@
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
     <x:t>BONCK, JON</x:t>
   </x:si>
   <x:si>
     <x:t>38</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
     <x:t>MEALER, ALEXANDRA</x:t>
   </x:si>
   <x:si>
@@ -183,51 +285,6 @@
     <x:t>22</x:t>
   </x:si>
   <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TORRES, RITCHIE JOHN</x:t>
   </x:si>
   <x:si>
@@ -339,9 +396,6 @@
     <x:t>11</x:t>
   </x:si>
   <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
     <x:t>PEKARSKY, STELLA</x:t>
   </x:si>
   <x:si>
@@ -366,36 +420,6 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
     <x:t>CARL, JERRY LEE, JR</x:t>
   </x:si>
   <x:si>
@@ -411,9 +435,6 @@
     <x:t>DELBENE, SUZAN K</x:t>
   </x:si>
   <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
     <x:t>STRICKLAND, MARILYN</x:t>
   </x:si>
   <x:si>
@@ -439,27 +460,6 @@
   </x:si>
   <x:si>
     <x:t>MCKINNEY, DONAVAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STANTON, GREG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCHRIER, KIM DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WARNER, MARK ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAGEMAN, HARRIET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -968,10 +968,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>2479136</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -979,22 +979,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>10015605</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,551 +1002,551 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>455146</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E6" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="E6" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="F6" s="1">
-        <x:v>7170138</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>400022</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>418058</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D9" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E9" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
       <x:c r="F9" s="1">
-        <x:v>80948</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="D10" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E10" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="F10" s="1">
-        <x:v>558813</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>1673736</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="F13" s="1">
-        <x:v>708828</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>282975</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>348433</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>771658</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>461942</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91656</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>426281</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>141263</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>615886</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>513868</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>487316</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>411748</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>12254527</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>735613</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>1419040</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>56045</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>12</x:v>
@@ -1554,252 +1554,252 @@
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D29" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F29" s="1">
-        <x:v>83860</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>262965</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>111599</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>109274</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>487174</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>106348</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>107940</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>172296</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>98455</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>516368</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>47162</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,252 +1807,252 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>382680</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>377124</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>380377</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>107387</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>4239904</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>557012</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>5259858</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>6471279</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1012792</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>20483</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>119844</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,804 +2060,804 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>285009</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>30220</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>91847</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>300000</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>550000</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>350000</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>350000</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>628597</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>221403</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>250000</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>350000</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B62" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C62" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="D62" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
-      <x:c r="B62" s="1" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="C62" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D62" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>350000</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="C63" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="C63" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>300000</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>500000</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B65" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B65" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>547042</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B66" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B66" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>455146</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>300000</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B68" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B68" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>7170138</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>189528</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B70" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B70" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>511996</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>300000</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B72" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B72" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>400022</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>113120</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
         <x:v>131</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>103020</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>508142</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>151713</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>1762153</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>34890</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D80" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="D80" s="1" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>418060</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>150000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>708827</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>268690</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>12</x:v>
@@ -2865,646 +2865,646 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>282975</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>348433</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>771658</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>461943</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B90" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B90" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>91656</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>426280</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>141263</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>616386</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B94" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B94" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>506917</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>157560</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>513868</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B97" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B97" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>487317</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>105040</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>550000</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B100" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B100" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>411748</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>12203100</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>350000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>628597</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>221403</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>250000</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>350000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>735613</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>300000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>2250000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>150000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>515838</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3553,1277 +3553,1277 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5">
       <x:c r="A69" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5">
       <x:c r="A74" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5">
       <x:c r="A76" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4868,968 +4868,968 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C70" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5870,354 +5870,354 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6462,7 +6462,7 @@
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>515838</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,10 +6550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,10 +6968,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>515838</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,424 +42,424 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
     <x:t>DEFEND AMERICAN JOBS</x:t>
   </x:si>
   <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUCHINCLOSS, JAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRICKLAND, MARILYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
     <x:t>DE LA CRUZ, CARLOS JR.</x:t>
   </x:si>
   <x:si>
     <x:t>35</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THANEDAR, SHRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODLANDER, MAGGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, DONAVAN</x:t>
   </x:si>
   <x:si>
     <x:t>MCKINNEY, AMANDA</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>STANTON, GREG</x:t>
   </x:si>
   <x:si>
     <x:t>AZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
     <x:t>SCHRIER, KIM DR.</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
     <x:t>WARNER, MARK ROBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
     <x:t>HAGEMAN, HARRIET</x:t>
   </x:si>
   <x:si>
     <x:t>WY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUCHINCLOSS, JAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRICKLAND, MARILYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANEDAR, SHRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODLANDER, MAGGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, DONAVAN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>616386</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -971,7 +971,7 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>506917</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -979,22 +979,22 @@
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B4" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C4" s="1" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C4" s="1" t="s">
-        <x:v>18</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>157560</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1008,16 +1008,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>513868</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -1031,16 +1031,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>487317</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -1048,22 +1048,22 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>105040</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1071,22 +1071,22 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>550000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>12</x:v>
@@ -1100,16 +1100,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>411748</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -1123,16 +1123,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>12203100</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1140,22 +1140,22 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E11" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="F11" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1163,22 +1163,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>350000</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1186,22 +1186,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>628597</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1209,22 +1209,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>221403</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1232,22 +1232,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>250000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1255,22 +1255,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>350000</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1278,22 +1278,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>350000</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1301,22 +1301,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>735613</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1324,19 +1324,19 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F19" s="1">
         <x:v>300000</x:v>
@@ -1347,22 +1347,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>2250000</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1370,22 +1370,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>150000</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1393,22 +1393,22 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="F22" s="1">
-        <x:v>515838</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1416,79 +1416,79 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="F23" s="1">
-        <x:v>817066</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>2479136</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>10015605</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>60</x:v>
@@ -1497,79 +1497,79 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>455146</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="F27" s="1">
-        <x:v>7170138</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F28" s="1">
+        <x:v>10015605</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
         <x:v>63</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F28" s="1">
-        <x:v>400022</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>418058</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>12</x:v>
@@ -1577,22 +1577,22 @@
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>80948</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1600,22 +1600,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>558813</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1623,22 +1623,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>1673736</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1646,22 +1646,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>430866</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1669,22 +1669,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>708828</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1692,22 +1692,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>282975</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1715,22 +1715,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>348433</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1738,22 +1738,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>771658</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1761,22 +1761,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>461942</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>12</x:v>
@@ -1784,22 +1784,22 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>91656</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,22 +1807,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>426281</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1830,22 +1830,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>141263</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1853,22 +1853,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>615886</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1876,22 +1876,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>513868</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1899,22 +1899,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>487316</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1922,22 +1922,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>411748</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1945,22 +1945,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>12254527</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1968,22 +1968,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>735613</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1991,22 +1991,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1419040</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -2014,45 +2014,45 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="B49" s="1" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="C49" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="B49" s="1" t="s">
+      <x:c r="D49" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E49" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="C49" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="D49" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E49" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F49" s="1">
-        <x:v>56045</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>83860</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,22 +2060,22 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>262965</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2083,45 +2083,45 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>111599</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>109274</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
         <x:v>12</x:v>
@@ -2129,22 +2129,22 @@
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>487174</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2152,22 +2152,22 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>106348</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2175,22 +2175,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>107940</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2198,22 +2198,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>172296</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2221,22 +2221,22 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>98455</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>12</x:v>
@@ -2244,22 +2244,22 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>516368</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2267,45 +2267,45 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D60" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E60" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="D60" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E60" s="1" t="s">
-        <x:v>11</x:v>
-      </x:c>
       <x:c r="F60" s="1">
-        <x:v>47162</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>382680</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2313,22 +2313,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
         <x:v>114</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>377124</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2336,45 +2336,45 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>380377</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>107387</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
         <x:v>12</x:v>
@@ -2382,22 +2382,22 @@
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>4239904</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2405,22 +2405,22 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>557012</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2428,22 +2428,22 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D67" s="1" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="D67" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>5259858</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2451,22 +2451,22 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>6471279</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2474,22 +2474,22 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
         <x:v>123</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>1012792</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>12</x:v>
@@ -2497,56 +2497,56 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>20483</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>119844</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
         <x:v>126</x:v>
@@ -2555,10 +2555,10 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>285009</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,68 +2566,68 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
         <x:v>127</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>30220</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>91847</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>300000</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
         <x:v>12</x:v>
@@ -2635,22 +2635,22 @@
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>550000</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2658,22 +2658,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>350000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2681,22 +2681,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>350000</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2704,22 +2704,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>628597</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2727,22 +2727,22 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>221403</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2750,22 +2750,22 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>250000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>12</x:v>
@@ -2773,22 +2773,22 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>350000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>12</x:v>
@@ -2796,22 +2796,22 @@
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>12</x:v>
@@ -2819,22 +2819,22 @@
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>300000</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>12</x:v>
@@ -2842,45 +2842,45 @@
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>500000</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>547042</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
         <x:v>12</x:v>
@@ -2888,22 +2888,22 @@
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>455146</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>12</x:v>
@@ -2911,22 +2911,22 @@
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>300000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
         <x:v>12</x:v>
@@ -2934,22 +2934,22 @@
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>7170138</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
         <x:v>12</x:v>
@@ -2957,22 +2957,22 @@
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>189528</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
         <x:v>12</x:v>
@@ -2980,22 +2980,22 @@
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>511996</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
         <x:v>12</x:v>
@@ -3003,22 +3003,22 @@
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>300000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
         <x:v>12</x:v>
@@ -3026,22 +3026,22 @@
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>400022</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
         <x:v>12</x:v>
@@ -3049,22 +3049,22 @@
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>113120</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
         <x:v>12</x:v>
@@ -3072,22 +3072,22 @@
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>103020</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
         <x:v>12</x:v>
@@ -3095,22 +3095,22 @@
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>508142</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
         <x:v>12</x:v>
@@ -3118,22 +3118,22 @@
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>151713</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
         <x:v>12</x:v>
@@ -3141,22 +3141,22 @@
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>430866</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
         <x:v>12</x:v>
@@ -3164,22 +3164,22 @@
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>1762153</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
         <x:v>12</x:v>
@@ -3187,22 +3187,22 @@
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>34890</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
         <x:v>12</x:v>
@@ -3210,22 +3210,22 @@
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>418060</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
         <x:v>12</x:v>
@@ -3239,16 +3239,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
         <x:v>12</x:v>
@@ -3256,22 +3256,22 @@
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>150000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
         <x:v>12</x:v>
@@ -3285,16 +3285,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>430866</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
         <x:v>12</x:v>
@@ -3308,16 +3308,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>708827</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
         <x:v>12</x:v>
@@ -3325,25 +3325,25 @@
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>268690</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -3354,16 +3354,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
         <x:v>12</x:v>
@@ -3377,16 +3377,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>348433</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
         <x:v>12</x:v>
@@ -3394,22 +3394,22 @@
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>771658</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
         <x:v>12</x:v>
@@ -3423,16 +3423,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>461943</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
         <x:v>12</x:v>
@@ -3446,16 +3446,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>91656</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
         <x:v>12</x:v>
@@ -3469,16 +3469,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>426280</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
         <x:v>12</x:v>
@@ -3486,22 +3486,22 @@
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>141263</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
         <x:v>12</x:v>
@@ -3553,13 +3553,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
@@ -3570,13 +3570,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
@@ -3587,13 +3587,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
@@ -3604,13 +3604,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
@@ -3621,13 +3621,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
@@ -3638,13 +3638,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
@@ -3655,13 +3655,13 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
@@ -3672,13 +3672,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
@@ -3689,13 +3689,13 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
@@ -3706,13 +3706,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>101</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>98</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
@@ -3723,13 +3723,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
@@ -3740,13 +3740,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
@@ -3757,13 +3757,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
@@ -3774,13 +3774,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
@@ -3791,13 +3791,13 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
@@ -3811,10 +3811,10 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
@@ -3825,13 +3825,13 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
@@ -3842,13 +3842,13 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
@@ -3859,13 +3859,13 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
@@ -3879,10 +3879,10 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
@@ -3896,10 +3896,10 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
@@ -3910,30 +3910,30 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
@@ -3944,13 +3944,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
@@ -3961,13 +3961,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
@@ -3978,13 +3978,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
@@ -3995,64 +3995,64 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
@@ -4063,13 +4063,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
@@ -4080,13 +4080,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
@@ -4097,13 +4097,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
@@ -4114,13 +4114,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
@@ -4131,13 +4131,13 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
@@ -4148,13 +4148,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
@@ -4165,13 +4165,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
@@ -4182,13 +4182,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
@@ -4199,13 +4199,13 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
@@ -4216,13 +4216,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
@@ -4233,13 +4233,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
@@ -4250,13 +4250,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
@@ -4267,13 +4267,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
@@ -4284,13 +4284,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
@@ -4301,30 +4301,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
@@ -4335,13 +4335,13 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
@@ -4352,13 +4352,13 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
@@ -4369,13 +4369,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="B50" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B50" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
@@ -4386,13 +4386,13 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
@@ -4403,13 +4403,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
@@ -4420,13 +4420,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
@@ -4437,13 +4437,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="C54" s="1" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="C54" s="1" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
@@ -4454,13 +4454,13 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
@@ -4471,13 +4471,13 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
@@ -4488,13 +4488,13 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
@@ -4505,13 +4505,13 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
@@ -4522,13 +4522,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B59" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="B59" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
@@ -4545,7 +4545,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
@@ -4559,10 +4559,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
@@ -4573,30 +4573,30 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
@@ -4613,7 +4613,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
@@ -4627,10 +4627,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
@@ -4641,13 +4641,13 @@
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
@@ -4658,13 +4658,13 @@
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B67" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="B67" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
@@ -4675,13 +4675,13 @@
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
@@ -4692,13 +4692,13 @@
     </x:row>
     <x:row r="69" spans="1:5">
       <x:c r="A69" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
@@ -4709,30 +4709,30 @@
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
@@ -4743,13 +4743,13 @@
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
@@ -4760,13 +4760,13 @@
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
@@ -4777,13 +4777,13 @@
     </x:row>
     <x:row r="74" spans="1:5">
       <x:c r="A74" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
@@ -4794,13 +4794,13 @@
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
@@ -4811,13 +4811,13 @@
     </x:row>
     <x:row r="76" spans="1:5">
       <x:c r="A76" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>515838</x:v>
@@ -4868,10 +4868,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -4882,10 +4882,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
@@ -4896,10 +4896,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
@@ -4910,10 +4910,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -4924,10 +4924,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -4938,10 +4938,10 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
@@ -4952,10 +4952,10 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
@@ -4966,10 +4966,10 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
@@ -4980,10 +4980,10 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
@@ -4994,10 +4994,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
@@ -5008,10 +5008,10 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
@@ -5022,10 +5022,10 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
@@ -5036,10 +5036,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
@@ -5050,10 +5050,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
@@ -5064,10 +5064,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
@@ -5078,10 +5078,10 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
@@ -5092,10 +5092,10 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
@@ -5106,10 +5106,10 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
@@ -5120,10 +5120,10 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
@@ -5134,10 +5134,10 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
@@ -5148,24 +5148,24 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
@@ -5176,10 +5176,10 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
@@ -5190,10 +5190,10 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
@@ -5204,52 +5204,52 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
@@ -5260,10 +5260,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
@@ -5274,10 +5274,10 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
@@ -5288,10 +5288,10 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
@@ -5302,10 +5302,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
@@ -5316,10 +5316,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
@@ -5330,10 +5330,10 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
@@ -5344,10 +5344,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
@@ -5358,10 +5358,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
@@ -5372,10 +5372,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
@@ -5386,10 +5386,10 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
@@ -5400,24 +5400,24 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
@@ -5428,10 +5428,10 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
@@ -5442,10 +5442,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
@@ -5456,10 +5456,10 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
@@ -5470,10 +5470,10 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
@@ -5484,10 +5484,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
@@ -5498,10 +5498,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
@@ -5512,10 +5512,10 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>45</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
@@ -5526,10 +5526,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
@@ -5540,10 +5540,10 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
@@ -5554,10 +5554,10 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
@@ -5568,10 +5568,10 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
@@ -5582,10 +5582,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
@@ -5599,7 +5599,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
@@ -5610,10 +5610,10 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
@@ -5624,24 +5624,24 @@
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
@@ -5655,7 +5655,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
@@ -5666,10 +5666,10 @@
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
@@ -5680,10 +5680,10 @@
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
@@ -5694,10 +5694,10 @@
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
@@ -5708,10 +5708,10 @@
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
@@ -5722,10 +5722,10 @@
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
@@ -5736,24 +5736,24 @@
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
@@ -5764,10 +5764,10 @@
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
@@ -5778,10 +5778,10 @@
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
@@ -5792,10 +5792,10 @@
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
@@ -5806,10 +5806,10 @@
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
@@ -5820,10 +5820,10 @@
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C70" s="1">
         <x:v>515838</x:v>
@@ -5870,7 +5870,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -5881,7 +5881,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -5892,7 +5892,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -5903,7 +5903,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -5914,7 +5914,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -5925,7 +5925,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -5936,18 +5936,18 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
@@ -5958,18 +5958,18 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
@@ -5980,7 +5980,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
@@ -5991,7 +5991,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
@@ -6002,7 +6002,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
@@ -6013,7 +6013,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
@@ -6024,7 +6024,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
@@ -6035,18 +6035,18 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
@@ -6057,7 +6057,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
@@ -6068,7 +6068,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
@@ -6079,7 +6079,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
@@ -6090,7 +6090,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
@@ -6101,7 +6101,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
@@ -6112,7 +6112,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
@@ -6123,7 +6123,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
@@ -6134,7 +6134,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
@@ -6145,18 +6145,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
@@ -6167,7 +6167,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
@@ -6178,18 +6178,18 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
@@ -6200,7 +6200,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
@@ -6211,7 +6211,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>515838</x:v>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6462,7 +6462,7 @@
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>515838</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,10 +6550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
         <x:v>27</x:v>
-      </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,10 +6968,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>515838</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,12 +42,249 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STANTON, GREG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCHRIER, KIM DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00915181</x:t>
   </x:si>
   <x:si>
     <x:t>FELLOWSHIP PAC</x:t>
   </x:si>
   <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WARNER, MARK ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
     <x:t>TORRES, RITCHIE JOHN</x:t>
   </x:si>
   <x:si>
@@ -57,126 +294,150 @@
     <x:t>NY</x:t>
   </x:si>
   <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
   </x:si>
   <x:si>
     <x:t>CARL, JERRY LEE, JR</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>AUCHINCLOSS, JAKE</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
     <x:t>MA</x:t>
   </x:si>
   <x:si>
     <x:t>HUIZENGA, WILLIAM P</x:t>
   </x:si>
   <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
     <x:t>DELBENE, SUZAN K</x:t>
   </x:si>
   <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
     <x:t>STRICKLAND, MARILYN</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>BEGICH, NICHOLAS III</x:t>
   </x:si>
   <x:si>
@@ -186,249 +447,9 @@
     <x:t>FRANKEL, LOIS J.</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
     <x:t>KINGSTON, JACK REP.</x:t>
   </x:si>
   <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
     <x:t>THANEDAR, SHRI</x:t>
   </x:si>
   <x:si>
@@ -439,27 +460,6 @@
   </x:si>
   <x:si>
     <x:t>MCKINNEY, DONAVAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STANTON, GREG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCHRIER, KIM DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WARNER, MARK ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAGEMAN, HARRIET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>300000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -968,10 +968,10 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>550000</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -985,16 +985,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D4" s="1" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D4" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>350000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1008,16 +1008,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
         <x:v>12</x:v>
@@ -1031,16 +1031,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="s">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>628597</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -1054,16 +1054,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D7" s="1" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="D7" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>221403</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
         <x:v>12</x:v>
@@ -1071,22 +1071,22 @@
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>250000</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
         <x:v>12</x:v>
@@ -1100,16 +1100,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>350000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
         <x:v>12</x:v>
@@ -1123,16 +1123,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>350000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
         <x:v>12</x:v>
@@ -1140,22 +1140,22 @@
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>300000</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
         <x:v>12</x:v>
@@ -1163,22 +1163,22 @@
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>500000</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
         <x:v>12</x:v>
@@ -1186,22 +1186,22 @@
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>547042</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1209,22 +1209,22 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>455146</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
         <x:v>12</x:v>
@@ -1232,22 +1232,22 @@
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>300000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
         <x:v>12</x:v>
@@ -1255,22 +1255,22 @@
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>7170138</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>12</x:v>
@@ -1278,22 +1278,22 @@
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>189528</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
         <x:v>12</x:v>
@@ -1301,22 +1301,22 @@
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>511996</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1324,22 +1324,22 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>300000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
         <x:v>12</x:v>
@@ -1347,22 +1347,22 @@
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>400022</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
         <x:v>12</x:v>
@@ -1370,22 +1370,22 @@
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>113120</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1393,22 +1393,22 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>103020</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
         <x:v>12</x:v>
@@ -1416,22 +1416,22 @@
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>508142</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>12</x:v>
@@ -1439,22 +1439,22 @@
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>151713</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>12</x:v>
@@ -1462,22 +1462,22 @@
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>430866</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>12</x:v>
@@ -1485,114 +1485,114 @@
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
       <x:c r="F26" s="1">
-        <x:v>817066</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="F27" s="1">
+        <x:v>817066</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
         <x:v>64</x:v>
-      </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E27" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F27" s="1">
-        <x:v>2479136</x:v>
-      </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>10015605</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>455146</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>7170138</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>12</x:v>
@@ -1600,22 +1600,22 @@
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>400022</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>12</x:v>
@@ -1623,22 +1623,22 @@
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>418058</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
         <x:v>12</x:v>
@@ -1646,22 +1646,22 @@
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>80948</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
         <x:v>12</x:v>
@@ -1669,22 +1669,22 @@
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>558813</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>12</x:v>
@@ -1692,22 +1692,22 @@
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>1673736</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
         <x:v>12</x:v>
@@ -1715,22 +1715,22 @@
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>430866</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
         <x:v>12</x:v>
@@ -1738,22 +1738,22 @@
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>708828</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
         <x:v>12</x:v>
@@ -1761,22 +1761,22 @@
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>282975</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
         <x:v>12</x:v>
@@ -1784,22 +1784,22 @@
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>348433</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,22 +1807,22 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>771658</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
         <x:v>12</x:v>
@@ -1830,22 +1830,22 @@
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C41" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C41" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D41" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>461942</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
         <x:v>12</x:v>
@@ -1853,22 +1853,22 @@
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>91656</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
         <x:v>12</x:v>
@@ -1876,22 +1876,22 @@
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>426281</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
         <x:v>12</x:v>
@@ -1899,22 +1899,22 @@
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>141263</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
         <x:v>12</x:v>
@@ -1922,22 +1922,22 @@
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>615886</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
         <x:v>12</x:v>
@@ -1945,22 +1945,22 @@
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>513868</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
         <x:v>12</x:v>
@@ -1968,22 +1968,22 @@
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>487316</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
         <x:v>12</x:v>
@@ -1991,22 +1991,22 @@
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>411748</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
         <x:v>12</x:v>
@@ -2014,22 +2014,22 @@
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>12254527</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>735613</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,22 +2060,22 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>1419040</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
         <x:v>12</x:v>
@@ -2083,68 +2083,68 @@
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>56045</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>83860</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>262965</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
         <x:v>12</x:v>
@@ -2152,22 +2152,22 @@
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>111599</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
         <x:v>12</x:v>
@@ -2175,22 +2175,22 @@
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>109274</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
         <x:v>12</x:v>
@@ -2198,22 +2198,22 @@
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>487174</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
         <x:v>12</x:v>
@@ -2221,22 +2221,22 @@
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>106348</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
         <x:v>12</x:v>
@@ -2244,22 +2244,22 @@
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>107940</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
         <x:v>12</x:v>
@@ -2267,22 +2267,22 @@
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>172296</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
         <x:v>12</x:v>
@@ -2290,22 +2290,22 @@
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>98455</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2313,22 +2313,22 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>516368</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
         <x:v>12</x:v>
@@ -2336,68 +2336,68 @@
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>47162</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>382680</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>377124</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
         <x:v>12</x:v>
@@ -2405,22 +2405,22 @@
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>380377</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
         <x:v>12</x:v>
@@ -2428,22 +2428,22 @@
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>107387</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2451,22 +2451,22 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>4239904</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
         <x:v>12</x:v>
@@ -2474,22 +2474,22 @@
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>557012</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
         <x:v>12</x:v>
@@ -2497,22 +2497,22 @@
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>5259858</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
         <x:v>12</x:v>
@@ -2520,22 +2520,22 @@
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>6471279</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
         <x:v>12</x:v>
@@ -2543,22 +2543,22 @@
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>1012792</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
         <x:v>12</x:v>
@@ -2566,91 +2566,91 @@
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>20483</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>119844</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>285009</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>30220</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
         <x:v>12</x:v>
@@ -2658,22 +2658,22 @@
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>91847</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
         <x:v>12</x:v>
@@ -2681,22 +2681,22 @@
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>1762153</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
         <x:v>12</x:v>
@@ -2704,22 +2704,22 @@
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>34890</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
         <x:v>12</x:v>
@@ -2727,22 +2727,22 @@
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>418060</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
         <x:v>12</x:v>
@@ -2750,22 +2750,22 @@
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
         <x:v>12</x:v>
@@ -2773,22 +2773,22 @@
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>150000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
         <x:v>12</x:v>
@@ -2796,22 +2796,22 @@
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>430866</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
         <x:v>12</x:v>
@@ -2819,22 +2819,22 @@
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>708827</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
         <x:v>12</x:v>
@@ -2842,45 +2842,45 @@
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>268690</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
         <x:v>12</x:v>
@@ -2888,22 +2888,22 @@
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>348433</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>12</x:v>
@@ -2911,22 +2911,22 @@
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>771658</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
         <x:v>12</x:v>
@@ -2934,22 +2934,22 @@
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>461943</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
         <x:v>12</x:v>
@@ -2957,22 +2957,22 @@
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>91656</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
         <x:v>12</x:v>
@@ -2980,22 +2980,22 @@
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>426280</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
         <x:v>12</x:v>
@@ -3003,22 +3003,22 @@
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>141263</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
         <x:v>12</x:v>
@@ -3026,22 +3026,22 @@
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>616386</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
         <x:v>12</x:v>
@@ -3049,22 +3049,22 @@
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>506917</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
         <x:v>12</x:v>
@@ -3072,22 +3072,22 @@
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>157560</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
         <x:v>12</x:v>
@@ -3095,22 +3095,22 @@
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D96" s="1" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="D96" s="1" t="s">
-        <x:v>42</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>513868</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
         <x:v>12</x:v>
@@ -3118,22 +3118,22 @@
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>487317</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
         <x:v>12</x:v>
@@ -3141,22 +3141,22 @@
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>105040</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
         <x:v>12</x:v>
@@ -3164,22 +3164,22 @@
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>550000</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
         <x:v>12</x:v>
@@ -3187,22 +3187,22 @@
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>411748</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
         <x:v>12</x:v>
@@ -3210,22 +3210,22 @@
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>12203100</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
         <x:v>12</x:v>
@@ -3239,16 +3239,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
         <x:v>12</x:v>
@@ -3256,22 +3256,22 @@
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>350000</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
         <x:v>12</x:v>
@@ -3279,22 +3279,22 @@
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>628597</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
         <x:v>12</x:v>
@@ -3308,16 +3308,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>221403</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
         <x:v>12</x:v>
@@ -3331,16 +3331,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>250000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
         <x:v>12</x:v>
@@ -3348,22 +3348,22 @@
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>350000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
         <x:v>12</x:v>
@@ -3377,16 +3377,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
         <x:v>12</x:v>
@@ -3394,22 +3394,22 @@
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>735613</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
         <x:v>12</x:v>
@@ -3417,25 +3417,25 @@
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>300000</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
@@ -3446,16 +3446,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>2250000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
         <x:v>12</x:v>
@@ -3469,16 +3469,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>150000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
         <x:v>12</x:v>
@@ -3486,22 +3486,22 @@
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C113" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D113" s="1" t="s">
         <x:v>33</x:v>
       </x:c>
-      <x:c r="C113" s="1" t="s">
-        <x:v>145</x:v>
-      </x:c>
-      <x:c r="D113" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>515838</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
         <x:v>12</x:v>
@@ -3553,13 +3553,13 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
@@ -3570,13 +3570,13 @@
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
@@ -3587,13 +3587,13 @@
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
@@ -3604,13 +3604,13 @@
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
@@ -3621,13 +3621,13 @@
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
@@ -3638,13 +3638,13 @@
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
@@ -3655,13 +3655,13 @@
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
@@ -3672,13 +3672,13 @@
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
@@ -3689,13 +3689,13 @@
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
@@ -3706,13 +3706,13 @@
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
@@ -3723,13 +3723,13 @@
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
@@ -3740,13 +3740,13 @@
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
@@ -3757,13 +3757,13 @@
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
@@ -3774,13 +3774,13 @@
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
@@ -3791,13 +3791,13 @@
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
@@ -3808,13 +3808,13 @@
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
@@ -3825,13 +3825,13 @@
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
@@ -3842,13 +3842,13 @@
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
@@ -3859,13 +3859,13 @@
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
@@ -3876,13 +3876,13 @@
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
@@ -3893,13 +3893,13 @@
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
@@ -3910,30 +3910,30 @@
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
@@ -3944,13 +3944,13 @@
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
@@ -3961,13 +3961,13 @@
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
@@ -3978,13 +3978,13 @@
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
@@ -3995,64 +3995,64 @@
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
@@ -4063,13 +4063,13 @@
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
@@ -4080,13 +4080,13 @@
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
@@ -4097,13 +4097,13 @@
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
@@ -4114,13 +4114,13 @@
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
@@ -4131,13 +4131,13 @@
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
@@ -4148,13 +4148,13 @@
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
@@ -4165,13 +4165,13 @@
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
@@ -4182,13 +4182,13 @@
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
@@ -4199,13 +4199,13 @@
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
@@ -4216,13 +4216,13 @@
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
@@ -4233,13 +4233,13 @@
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
@@ -4250,13 +4250,13 @@
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
@@ -4267,13 +4267,13 @@
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
@@ -4284,13 +4284,13 @@
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
@@ -4301,30 +4301,30 @@
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
@@ -4335,13 +4335,13 @@
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
@@ -4352,13 +4352,13 @@
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
@@ -4369,13 +4369,13 @@
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
@@ -4386,13 +4386,13 @@
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
@@ -4403,13 +4403,13 @@
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
@@ -4420,13 +4420,13 @@
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
@@ -4437,13 +4437,13 @@
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
@@ -4454,13 +4454,13 @@
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
@@ -4471,13 +4471,13 @@
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
@@ -4488,13 +4488,13 @@
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
@@ -4505,13 +4505,13 @@
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
@@ -4522,13 +4522,13 @@
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
@@ -4539,13 +4539,13 @@
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
@@ -4556,13 +4556,13 @@
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
@@ -4573,30 +4573,30 @@
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
@@ -4607,13 +4607,13 @@
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
@@ -4624,13 +4624,13 @@
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
@@ -4641,13 +4641,13 @@
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
@@ -4658,13 +4658,13 @@
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
@@ -4675,13 +4675,13 @@
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
@@ -4692,13 +4692,13 @@
     </x:row>
     <x:row r="69" spans="1:5">
       <x:c r="A69" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
@@ -4709,30 +4709,30 @@
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
@@ -4743,13 +4743,13 @@
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
@@ -4760,13 +4760,13 @@
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
@@ -4777,13 +4777,13 @@
     </x:row>
     <x:row r="74" spans="1:5">
       <x:c r="A74" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
@@ -4794,13 +4794,13 @@
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
@@ -4811,13 +4811,13 @@
     </x:row>
     <x:row r="76" spans="1:5">
       <x:c r="A76" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>515838</x:v>
@@ -4868,10 +4868,10 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -4882,10 +4882,10 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
@@ -4896,10 +4896,10 @@
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
@@ -4910,10 +4910,10 @@
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -4924,10 +4924,10 @@
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -4938,10 +4938,10 @@
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
@@ -4952,10 +4952,10 @@
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
@@ -4966,10 +4966,10 @@
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
@@ -4980,10 +4980,10 @@
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
@@ -4994,10 +4994,10 @@
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
@@ -5008,10 +5008,10 @@
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
@@ -5022,10 +5022,10 @@
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
@@ -5036,10 +5036,10 @@
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
@@ -5050,10 +5050,10 @@
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
@@ -5064,10 +5064,10 @@
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
@@ -5078,10 +5078,10 @@
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
@@ -5092,10 +5092,10 @@
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
@@ -5106,10 +5106,10 @@
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
@@ -5120,10 +5120,10 @@
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
@@ -5134,10 +5134,10 @@
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
@@ -5148,24 +5148,24 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
@@ -5176,10 +5176,10 @@
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
@@ -5190,10 +5190,10 @@
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
@@ -5204,52 +5204,52 @@
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
@@ -5260,10 +5260,10 @@
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
@@ -5274,10 +5274,10 @@
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
@@ -5288,10 +5288,10 @@
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
@@ -5302,10 +5302,10 @@
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
@@ -5316,10 +5316,10 @@
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
@@ -5330,10 +5330,10 @@
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
@@ -5344,10 +5344,10 @@
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
@@ -5358,10 +5358,10 @@
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
@@ -5372,10 +5372,10 @@
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
@@ -5386,10 +5386,10 @@
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
@@ -5400,24 +5400,24 @@
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
@@ -5428,10 +5428,10 @@
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
@@ -5442,10 +5442,10 @@
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
@@ -5456,10 +5456,10 @@
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
@@ -5470,10 +5470,10 @@
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
@@ -5484,10 +5484,10 @@
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
@@ -5498,10 +5498,10 @@
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
@@ -5512,10 +5512,10 @@
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
@@ -5526,10 +5526,10 @@
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
@@ -5540,10 +5540,10 @@
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
@@ -5554,10 +5554,10 @@
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
@@ -5568,10 +5568,10 @@
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
@@ -5582,10 +5582,10 @@
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
@@ -5596,10 +5596,10 @@
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
@@ -5610,10 +5610,10 @@
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
@@ -5624,24 +5624,24 @@
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
@@ -5652,10 +5652,10 @@
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
@@ -5666,10 +5666,10 @@
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
@@ -5680,10 +5680,10 @@
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
@@ -5694,10 +5694,10 @@
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
@@ -5708,10 +5708,10 @@
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
@@ -5722,10 +5722,10 @@
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
@@ -5736,24 +5736,24 @@
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
@@ -5764,10 +5764,10 @@
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
@@ -5778,10 +5778,10 @@
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
@@ -5792,10 +5792,10 @@
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
@@ -5806,10 +5806,10 @@
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
@@ -5820,10 +5820,10 @@
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C70" s="1">
         <x:v>515838</x:v>
@@ -5870,7 +5870,7 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -5881,7 +5881,7 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -5892,7 +5892,7 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -5903,7 +5903,7 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -5914,7 +5914,7 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -5925,7 +5925,7 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -5936,18 +5936,18 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
@@ -5958,18 +5958,18 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
@@ -5980,7 +5980,7 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
@@ -5991,7 +5991,7 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
@@ -6002,7 +6002,7 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
@@ -6013,7 +6013,7 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
@@ -6024,7 +6024,7 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
@@ -6035,18 +6035,18 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
@@ -6057,7 +6057,7 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
@@ -6068,7 +6068,7 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
@@ -6079,7 +6079,7 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
@@ -6090,7 +6090,7 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
@@ -6101,7 +6101,7 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
@@ -6112,7 +6112,7 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
@@ -6123,7 +6123,7 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
@@ -6134,7 +6134,7 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
@@ -6145,18 +6145,18 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
@@ -6167,7 +6167,7 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
@@ -6178,18 +6178,18 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
@@ -6200,7 +6200,7 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
@@ -6211,7 +6211,7 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>515838</x:v>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6462,7 +6462,7 @@
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>515838</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,10 +6550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,10 +6968,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>515838</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,30 +42,135 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
     <x:t>DEFEND AMERICAN JOBS</x:t>
   </x:si>
   <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
     <x:t>MEALER, ALEXANDRA</x:t>
   </x:si>
   <x:si>
     <x:t>09</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>SELL, TOM</x:t>
   </x:si>
   <x:si>
@@ -84,382 +189,277 @@
     <x:t>35</x:t>
   </x:si>
   <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUCHINCLOSS, JAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRICKLAND, MARILYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THANEDAR, SHRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODLANDER, MAGGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, DONAVAN</x:t>
+  </x:si>
+  <x:si>
     <x:t>MCKINNEY, AMANDA</x:t>
   </x:si>
   <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>STANTON, GREG</x:t>
   </x:si>
   <x:si>
     <x:t>AZ</x:t>
   </x:si>
   <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
     <x:t>SCHRIER, KIM DR.</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
     <x:t>WARNER, MARK ROBERT</x:t>
   </x:si>
   <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
     <x:t>HAGEMAN, HARRIET</x:t>
   </x:si>
   <x:si>
     <x:t>WY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUCHINCLOSS, JAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRICKLAND, MARILYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANEDAR, SHRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODLANDER, MAGGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, DONAVAN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>461943</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -971,7 +971,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>91656</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -994,7 +994,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>426280</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,804 +1002,804 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>141263</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>616386</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>506917</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>157560</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>513868</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>487317</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>105040</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>550000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>411748</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>12203100</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>350000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>350000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>37</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="F17" s="1">
-        <x:v>628597</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>221403</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>250000</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>350000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>350000</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>735613</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>300000</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>2250000</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>150000</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>515838</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>817066</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2479136</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>10015605</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>455146</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>7170138</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>400022</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>418058</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>80948</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>558813</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>1673736</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>430866</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>708828</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>282975</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,229 +1807,229 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>348433</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>771658</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>461942</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>91656</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>426281</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>141263</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>615886</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>513868</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>487316</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>411748</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>12254527</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,804 +2060,804 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>735613</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>1419040</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>56045</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>83860</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>262965</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>111599</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>109274</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C58" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D58" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E58" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C58" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="D58" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E58" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="F58" s="1">
-        <x:v>487174</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C59" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="D59" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E59" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C59" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="D59" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="E59" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="F59" s="1">
-        <x:v>106348</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>107940</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>172296</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>98455</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>516368</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>47162</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>382680</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>377124</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>380377</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B68" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C68" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D68" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B68" s="1" t="s">
+      <x:c r="E68" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C68" s="1" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D68" s="1" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="E68" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="F68" s="1">
-        <x:v>107387</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>4239904</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>557012</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>5259858</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>6471279</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>1012792</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>20483</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>119844</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>285009</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>30220</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>91847</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>300000</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>550000</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>350000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>350000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>628597</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>221403</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>250000</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>12</x:v>
@@ -2865,646 +2865,646 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>350000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>350000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>300000</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>500000</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>547042</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>455146</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>300000</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="D93" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E93" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="D93" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="E93" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
       <x:c r="F93" s="1">
-        <x:v>7170138</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>189528</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>511996</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>300000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>400022</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>113120</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>103020</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>508142</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>151713</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>1762153</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C104" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D104" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E104" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C104" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D104" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E104" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="F104" s="1">
-        <x:v>34890</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>418060</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>80948</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>150000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>430866</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>708827</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>268690</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>282975</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>348433</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>771658</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3553,1277 +3553,1277 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5">
       <x:c r="A69" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5">
       <x:c r="A74" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5">
       <x:c r="A76" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4868,968 +4868,968 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C70" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5870,354 +5870,354 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6462,7 +6462,7 @@
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>515838</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,10 +6550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,10 +6968,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>515838</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,162 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00836221</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DEFEND AMERICAN JOBS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEALER, ALEXANDRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>09</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUPPORT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOBER, CHRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEHLS, TREVER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STANTON, GREG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCHRIER, KIM DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WARNER, MARK ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00835959</x:t>
   </x:si>
   <x:si>
@@ -69,36 +225,15 @@
     <x:t>STRATTON, JULIANA</x:t>
   </x:si>
   <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00836221</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DEFEND AMERICAN JOBS</x:t>
-  </x:si>
-  <x:si>
     <x:t>FULLER, CLAY</x:t>
   </x:si>
   <x:si>
     <x:t>14</x:t>
   </x:si>
   <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SUPPORT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
     <x:t>06</x:t>
   </x:si>
   <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
     <x:t>MOORE, BLAKE</x:t>
   </x:si>
   <x:si>
@@ -135,99 +270,21 @@
     <x:t>GAINES, HOUSTON</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
     <x:t>SMITH, ADRIAN</x:t>
   </x:si>
   <x:si>
     <x:t>03</x:t>
   </x:si>
   <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
     <x:t>BONCK, JON</x:t>
   </x:si>
   <x:si>
     <x:t>38</x:t>
   </x:si>
   <x:si>
-    <x:t>TX</x:t>
-  </x:si>
-  <x:si>
     <x:t>STEINMANN, JESSICA HART</x:t>
   </x:si>
   <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MEALER, ALEXANDRA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>09</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOBER, CHRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEHLS, TREVER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
-  </x:si>
-  <x:si>
     <x:t>TORRES, RITCHIE JOHN</x:t>
   </x:si>
   <x:si>
@@ -339,9 +396,6 @@
     <x:t>11</x:t>
   </x:si>
   <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
     <x:t>PEKARSKY, STELLA</x:t>
   </x:si>
   <x:si>
@@ -366,36 +420,6 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
     <x:t>CARL, JERRY LEE, JR</x:t>
   </x:si>
   <x:si>
@@ -411,9 +435,6 @@
     <x:t>DELBENE, SUZAN K</x:t>
   </x:si>
   <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
     <x:t>STRICKLAND, MARILYN</x:t>
   </x:si>
   <x:si>
@@ -439,27 +460,6 @@
   </x:si>
   <x:si>
     <x:t>MCKINNEY, DONAVAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STANTON, GREG</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCHRIER, KIM DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WARNER, MARK ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAGEMAN, HARRIET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WY</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>817066</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -971,7 +971,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>2479136</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
         <x:v>12</x:v>
@@ -994,7 +994,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>10015605</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
         <x:v>12</x:v>
@@ -1002,804 +1002,804 @@
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B5" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C5" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B5" s="1" t="s">
+      <x:c r="D5" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C5" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D5" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>455146</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>7170138</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>400022</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>418058</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>80948</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>558813</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>1673736</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>430866</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>708828</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>282975</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="1">
-        <x:v>348433</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>771658</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>461942</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>91656</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>426281</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>141263</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>615886</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>513868</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>487316</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>411748</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>12254527</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>735613</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>1419040</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>56045</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B29" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="C29" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>83860</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C30" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C30" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>262965</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>111599</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F32" s="1">
-        <x:v>109274</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>487174</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>106348</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>107940</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>172296</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>98455</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>516368</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>47162</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
         <x:v>12</x:v>
@@ -1807,229 +1807,229 @@
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>382680</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>377124</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>380377</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>107387</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>4239904</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>557012</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>5259858</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>6471279</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>1012792</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>20483</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
         <x:v>12</x:v>
@@ -2037,22 +2037,22 @@
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>119844</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
         <x:v>12</x:v>
@@ -2060,804 +2060,804 @@
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>285009</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>30220</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F53" s="1">
-        <x:v>91847</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>300000</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F55" s="1">
-        <x:v>550000</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>350000</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>350000</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>628597</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>221403</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>250000</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>350000</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>350000</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>300000</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>500000</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>547042</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>455146</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C67" s="1" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="C67" s="1" t="s">
-        <x:v>19</x:v>
-      </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>300000</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>7170138</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>189528</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>511996</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>300000</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>400022</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>113120</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>103020</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>508142</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>151713</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>430866</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>1762153</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>34890</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>418060</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>80948</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>150000</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>430866</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D84" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D84" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>708827</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>268690</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
         <x:v>12</x:v>
@@ -2865,646 +2865,646 @@
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>282975</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>348433</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>771658</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>461943</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>91656</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>426280</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>141263</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>616386</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>506917</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>157560</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>513868</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>487317</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>105040</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>550000</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>411748</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C101" s="1" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="D101" s="1" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="C101" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D101" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>12203100</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>350000</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>628597</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>221403</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>250000</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>350000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>350000</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>735613</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>300000</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>2250000</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>150000</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>515838</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3553,1277 +3553,1277 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:5">
       <x:c r="A10" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:5">
       <x:c r="A11" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:5">
       <x:c r="A12" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:5">
       <x:c r="A13" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:5">
       <x:c r="A14" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>98</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>79</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:5">
       <x:c r="A15" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:5">
       <x:c r="A16" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5">
       <x:c r="A18" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5">
       <x:c r="A19" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:5">
       <x:c r="A20" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>430866</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:5">
       <x:c r="A21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>861732</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:5">
       <x:c r="A22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:5">
       <x:c r="A23" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:5">
       <x:c r="A24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:5">
       <x:c r="A25" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:5">
       <x:c r="A26" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>285009</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:5">
       <x:c r="A27" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>30220</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:5">
       <x:c r="A28" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:5">
       <x:c r="A29" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:5">
       <x:c r="A30" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:5">
       <x:c r="A31" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D31" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:5">
       <x:c r="A32" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D32" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:5">
       <x:c r="A33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D33" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:5">
       <x:c r="A34" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D34" s="1">
         <x:v>1257194</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:5">
       <x:c r="A35" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D35" s="1">
         <x:v>442806</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:5">
       <x:c r="A36" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D36" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:5">
       <x:c r="A37" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D37" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:5">
       <x:c r="A38" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D38" s="1">
         <x:v>500000</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:5">
       <x:c r="A39" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D39" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:5">
       <x:c r="A40" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D40" s="1">
         <x:v>98455</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:5">
       <x:c r="A41" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D41" s="1">
         <x:v>5259858</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:5">
       <x:c r="A42" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D42" s="1">
         <x:v>172296</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:5">
       <x:c r="A43" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D43" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:5">
       <x:c r="A44" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D44" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:5">
       <x:c r="A45" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D45" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:5">
       <x:c r="A46" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D46" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:5">
       <x:c r="A47" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D47" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:5">
       <x:c r="A48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D48" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:5">
       <x:c r="A49" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D49" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:5">
       <x:c r="A50" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D50" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:5">
       <x:c r="A51" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D51" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:5">
       <x:c r="A52" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D52" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:5">
       <x:c r="A53" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D53" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="E53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:5">
       <x:c r="A54" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D54" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:5">
       <x:c r="A55" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C55" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D55" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="E55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:5">
       <x:c r="A56" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C56" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D56" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:5">
       <x:c r="A57" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D57" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:5">
       <x:c r="A58" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D58" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:5">
       <x:c r="A59" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D59" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:5">
       <x:c r="A60" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D60" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:5">
       <x:c r="A61" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D61" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:5">
       <x:c r="A62" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D62" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:5">
       <x:c r="A63" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D63" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:5">
       <x:c r="A64" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D64" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:5">
       <x:c r="A65" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D65" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:5">
       <x:c r="A66" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D66" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:5">
       <x:c r="A67" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D67" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:5">
       <x:c r="A68" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D68" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:5">
       <x:c r="A69" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D69" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:5">
       <x:c r="A70" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D70" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:5">
       <x:c r="A71" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D71" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:5">
       <x:c r="A72" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D72" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:5">
       <x:c r="A73" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D73" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:5">
       <x:c r="A74" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D74" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:5">
       <x:c r="A75" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D75" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:5">
       <x:c r="A76" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D76" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4868,968 +4868,968 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>377124</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>487174</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>106348</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>380377</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>107387</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>107940</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>558813</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1673736</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>151713</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1292598</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1417655</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>4239904</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>1210292</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>315229</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>10135449</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>817066</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:4">
       <x:c r="A28" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>2479136</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:4">
       <x:c r="A29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>557012</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:4">
       <x:c r="A30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>83860</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:4">
       <x:c r="A31" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:4">
       <x:c r="A32" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>1700000</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:4">
       <x:c r="A33" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>14340276</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:4">
       <x:c r="A34" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:4">
       <x:c r="A35" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:4">
       <x:c r="A36" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5530609</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:4">
       <x:c r="A37" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>516368</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:4">
       <x:c r="A38" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>91847</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:4">
       <x:c r="A39" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>511996</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:4">
       <x:c r="A40" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:4">
       <x:c r="A41" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1762153</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:4">
       <x:c r="A42" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:4">
       <x:c r="A43" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>700000</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:4">
       <x:c r="A44" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>565950</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:4">
       <x:c r="A45" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C45" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:4">
       <x:c r="A46" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C46" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:4">
       <x:c r="A47" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C47" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:4">
       <x:c r="A48" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C48" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:4">
       <x:c r="A49" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C49" s="1">
         <x:v>1100000</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:4">
       <x:c r="A50" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C50" s="1">
         <x:v>974633</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:4">
       <x:c r="A51" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C51" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:4">
       <x:c r="A52" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C52" s="1">
         <x:v>2750000</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:4">
       <x:c r="A53" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C53" s="1">
         <x:v>1543316</x:v>
       </x:c>
       <x:c r="D53" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:4">
       <x:c r="A54" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C54" s="1">
         <x:v>923885</x:v>
       </x:c>
       <x:c r="D54" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
       <x:c r="A55" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C55" s="1">
         <x:v>183312</x:v>
       </x:c>
       <x:c r="D55" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:4">
       <x:c r="A56" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C56" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="D56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C57" s="1">
         <x:v>6471279</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C58" s="1">
         <x:v>852561</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C59" s="1">
         <x:v>282526</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C60" s="1">
         <x:v>1232272</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C61" s="1">
         <x:v>696866</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C62" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C63" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C64" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C65" s="1">
         <x:v>1012792</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:4">
       <x:c r="A66" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C66" s="1">
         <x:v>113120</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:4">
       <x:c r="A67" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C67" s="1">
         <x:v>506917</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:4">
       <x:c r="A68" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C68" s="1">
         <x:v>105040</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:4">
       <x:c r="A69" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C69" s="1">
         <x:v>103020</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:4">
       <x:c r="A70" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C70" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5870,354 +5870,354 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>56045</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>8860449</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>13431651</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>956101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1027736</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>16040276</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>1200000</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>189528</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>6046977</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>268690</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>2365996</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>161896</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>1265950</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>150000</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>297855</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>2019040</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>2071226</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>2074633</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>823496</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>47162</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>14936017</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B29" s="1">
         <x:v>800044</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B30" s="1">
         <x:v>20483</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B31" s="1">
         <x:v>1162792</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B32" s="1">
         <x:v>828097</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B33" s="1">
         <x:v>515838</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -6254,7 +6254,7 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B2" s="1">
         <x:v>508142</x:v>
@@ -6262,7 +6262,7 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B3" s="1">
         <x:v>25704669</x:v>
@@ -6270,7 +6270,7 @@
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B4" s="1">
         <x:v>836118</x:v>
@@ -6278,7 +6278,7 @@
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B5" s="1">
         <x:v>157560</x:v>
@@ -6286,7 +6286,7 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B6" s="1">
         <x:v>2169903</x:v>
@@ -6294,7 +6294,7 @@
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B7" s="1">
         <x:v>2384262</x:v>
@@ -6302,7 +6302,7 @@
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B8" s="1">
         <x:v>8916494</x:v>
@@ -6310,7 +6310,7 @@
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B9" s="1">
         <x:v>14387752</x:v>
@@ -6318,7 +6318,7 @@
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B10" s="1">
         <x:v>1027736</x:v>
@@ -6326,7 +6326,7 @@
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B11" s="1">
         <x:v>16040276</x:v>
@@ -6334,7 +6334,7 @@
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B12" s="1">
         <x:v>1200000</x:v>
@@ -6342,7 +6342,7 @@
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B13" s="1">
         <x:v>189528</x:v>
@@ -6350,7 +6350,7 @@
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B14" s="1">
         <x:v>6046977</x:v>
@@ -6358,7 +6358,7 @@
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B15" s="1">
         <x:v>2634686</x:v>
@@ -6366,7 +6366,7 @@
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B16" s="1">
         <x:v>161896</x:v>
@@ -6374,7 +6374,7 @@
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B17" s="1">
         <x:v>1265950</x:v>
@@ -6382,7 +6382,7 @@
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B18" s="1">
         <x:v>150000</x:v>
@@ -6390,7 +6390,7 @@
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="B19" s="1">
         <x:v>297855</x:v>
@@ -6398,7 +6398,7 @@
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B20" s="1">
         <x:v>2019040</x:v>
@@ -6406,7 +6406,7 @@
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="1">
         <x:v>2071226</x:v>
@@ -6414,7 +6414,7 @@
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B22" s="1">
         <x:v>2074633</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B23" s="1">
         <x:v>823496</x:v>
@@ -6430,7 +6430,7 @@
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B24" s="1">
         <x:v>14983179</x:v>
@@ -6438,7 +6438,7 @@
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B25" s="1">
         <x:v>800044</x:v>
@@ -6446,7 +6446,7 @@
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B26" s="1">
         <x:v>1183275</x:v>
@@ -6454,7 +6454,7 @@
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B27" s="1">
         <x:v>828097</x:v>
@@ -6462,7 +6462,7 @@
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B28" s="1">
         <x:v>515838</x:v>
@@ -6506,10 +6506,10 @@
     </x:row>
     <x:row r="2" spans="1:3">
       <x:c r="A2" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C2" s="1">
         <x:v>508142</x:v>
@@ -6517,10 +6517,10 @@
     </x:row>
     <x:row r="3" spans="1:3">
       <x:c r="A3" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C3" s="1">
         <x:v>25004669</x:v>
@@ -6528,10 +6528,10 @@
     </x:row>
     <x:row r="4" spans="1:3">
       <x:c r="A4" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C4" s="1">
         <x:v>700000</x:v>
@@ -6539,10 +6539,10 @@
     </x:row>
     <x:row r="5" spans="1:3">
       <x:c r="A5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C5" s="1">
         <x:v>836118</x:v>
@@ -6550,10 +6550,10 @@
     </x:row>
     <x:row r="6" spans="1:3">
       <x:c r="A6" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C6" s="1">
         <x:v>157560</x:v>
@@ -6561,10 +6561,10 @@
     </x:row>
     <x:row r="7" spans="1:3">
       <x:c r="A7" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C7" s="1">
         <x:v>2169903</x:v>
@@ -6572,10 +6572,10 @@
     </x:row>
     <x:row r="8" spans="1:3">
       <x:c r="A8" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C8" s="1">
         <x:v>2232549</x:v>
@@ -6583,10 +6583,10 @@
     </x:row>
     <x:row r="9" spans="1:3">
       <x:c r="A9" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C9" s="1">
         <x:v>151713</x:v>
@@ -6594,10 +6594,10 @@
     </x:row>
     <x:row r="10" spans="1:3">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3620545</x:v>
@@ -6605,10 +6605,10 @@
     </x:row>
     <x:row r="11" spans="1:3">
       <x:c r="A11" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1000000</x:v>
@@ -6616,10 +6616,10 @@
     </x:row>
     <x:row r="12" spans="1:3">
       <x:c r="A12" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>4295949</x:v>
@@ -6627,10 +6627,10 @@
     </x:row>
     <x:row r="13" spans="1:3">
       <x:c r="A13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>13311807</x:v>
@@ -6638,10 +6638,10 @@
     </x:row>
     <x:row r="14" spans="1:3">
       <x:c r="A14" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="1">
         <x:v>1075945</x:v>
@@ -6649,10 +6649,10 @@
     </x:row>
     <x:row r="15" spans="1:3">
       <x:c r="A15" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>1027736</x:v>
@@ -6660,10 +6660,10 @@
     </x:row>
     <x:row r="16" spans="1:3">
       <x:c r="A16" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>14340276</x:v>
@@ -6671,10 +6671,10 @@
     </x:row>
     <x:row r="17" spans="1:3">
       <x:c r="A17" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>1700000</x:v>
@@ -6682,10 +6682,10 @@
     </x:row>
     <x:row r="18" spans="1:3">
       <x:c r="A18" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1200000</x:v>
@@ -6693,10 +6693,10 @@
     </x:row>
     <x:row r="19" spans="1:3">
       <x:c r="A19" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>189528</x:v>
@@ -6704,10 +6704,10 @@
     </x:row>
     <x:row r="20" spans="1:3">
       <x:c r="A20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>6046977</x:v>
@@ -6715,10 +6715,10 @@
     </x:row>
     <x:row r="21" spans="1:3">
       <x:c r="A21" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>511996</x:v>
@@ -6726,10 +6726,10 @@
     </x:row>
     <x:row r="22" spans="1:3">
       <x:c r="A22" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C22" s="1">
         <x:v>91847</x:v>
@@ -6737,10 +6737,10 @@
     </x:row>
     <x:row r="23" spans="1:3">
       <x:c r="A23" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C23" s="1">
         <x:v>2030843</x:v>
@@ -6748,10 +6748,10 @@
     </x:row>
     <x:row r="24" spans="1:3">
       <x:c r="A24" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C24" s="1">
         <x:v>161896</x:v>
@@ -6759,10 +6759,10 @@
     </x:row>
     <x:row r="25" spans="1:3">
       <x:c r="A25" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C25" s="1">
         <x:v>565950</x:v>
@@ -6770,10 +6770,10 @@
     </x:row>
     <x:row r="26" spans="1:3">
       <x:c r="A26" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C26" s="1">
         <x:v>700000</x:v>
@@ -6781,10 +6781,10 @@
     </x:row>
     <x:row r="27" spans="1:3">
       <x:c r="A27" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C27" s="1">
         <x:v>150000</x:v>
@@ -6792,10 +6792,10 @@
     </x:row>
     <x:row r="28" spans="1:3">
       <x:c r="A28" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C28" s="1">
         <x:v>297855</x:v>
@@ -6803,10 +6803,10 @@
     </x:row>
     <x:row r="29" spans="1:3">
       <x:c r="A29" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C29" s="1">
         <x:v>600000</x:v>
@@ -6814,10 +6814,10 @@
     </x:row>
     <x:row r="30" spans="1:3">
       <x:c r="A30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C30" s="1">
         <x:v>1419040</x:v>
@@ -6825,10 +6825,10 @@
     </x:row>
     <x:row r="31" spans="1:3">
       <x:c r="A31" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C31" s="1">
         <x:v>1471226</x:v>
@@ -6836,10 +6836,10 @@
     </x:row>
     <x:row r="32" spans="1:3">
       <x:c r="A32" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C32" s="1">
         <x:v>600000</x:v>
@@ -6847,10 +6847,10 @@
     </x:row>
     <x:row r="33" spans="1:3">
       <x:c r="A33" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C33" s="1">
         <x:v>974633</x:v>
@@ -6858,10 +6858,10 @@
     </x:row>
     <x:row r="34" spans="1:3">
       <x:c r="A34" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C34" s="1">
         <x:v>1100000</x:v>
@@ -6869,10 +6869,10 @@
     </x:row>
     <x:row r="35" spans="1:3">
       <x:c r="A35" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C35" s="1">
         <x:v>823496</x:v>
@@ -6880,10 +6880,10 @@
     </x:row>
     <x:row r="36" spans="1:3">
       <x:c r="A36" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C36" s="1">
         <x:v>5714738</x:v>
@@ -6891,10 +6891,10 @@
     </x:row>
     <x:row r="37" spans="1:3">
       <x:c r="A37" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C37" s="1">
         <x:v>2750000</x:v>
@@ -6902,10 +6902,10 @@
     </x:row>
     <x:row r="38" spans="1:3">
       <x:c r="A38" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C38" s="1">
         <x:v>6518441</x:v>
@@ -6913,10 +6913,10 @@
     </x:row>
     <x:row r="39" spans="1:3">
       <x:c r="A39" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C39" s="1">
         <x:v>800044</x:v>
@@ -6924,10 +6924,10 @@
     </x:row>
     <x:row r="40" spans="1:3">
       <x:c r="A40" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C40" s="1">
         <x:v>150000</x:v>
@@ -6935,10 +6935,10 @@
     </x:row>
     <x:row r="41" spans="1:3">
       <x:c r="A41" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C41" s="1">
         <x:v>1033275</x:v>
@@ -6946,10 +6946,10 @@
     </x:row>
     <x:row r="42" spans="1:3">
       <x:c r="A42" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C42" s="1">
         <x:v>506917</x:v>
@@ -6957,10 +6957,10 @@
     </x:row>
     <x:row r="43" spans="1:3">
       <x:c r="A43" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C43" s="1">
         <x:v>321180</x:v>
@@ -6968,10 +6968,10 @@
     </x:row>
     <x:row r="44" spans="1:3">
       <x:c r="A44" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C44" s="1">
         <x:v>515838</x:v>

--- a/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
+++ b/reports/pro-crypto/pro-crypto-independent-expenditure-region.xlsx
@@ -42,6 +42,24 @@
     <x:t>expenditure_description</x:t>
   </x:si>
   <x:si>
+    <x:t>C00835959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIRSHAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRATTON, JULIANA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OPPOSE</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00836221</x:t>
   </x:si>
   <x:si>
@@ -60,406 +78,388 @@
     <x:t>SUPPORT</x:t>
   </x:si>
   <x:si>
+    <x:t>SELL, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00848440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PROTECT PROGRESS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENENDEZ, ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>08</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN, ALEXANDER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00915181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FELLOWSHIP PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BARR, GARLAND ANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CARL, JERRY LEE, JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, DONAVAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GOODLANDER, MAGGIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FORD, LA SHAWN K</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAIRD, JAMES R DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERN, KEVIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCOTT, DAVID ALBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUDZINSKI, NIKKI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LOFGREN, ZOE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BOAFO, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALKINSHAW, JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RICKETTS, PETE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JACK REP.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FULLER, CLAY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, TIM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, RANDY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SMITH, ADRIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOORE, FELIX BARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TORRES, RITCHIE JOHN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BAREEBE, QUINCY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCGUIRE, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORREA, LOU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>46</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BONCK, JON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SIMON, LATEEFAH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SOLIS, HILDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GRAHAM, LINDSEY O.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AUCHINCLOSS, JAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FRANKEL, LOIS J.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SCHRIER, KIM DR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KINGSTON, JAMES MORRIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GAINES, HOUSTON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELANEY, APRIL MCCLAIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KELLY, ROBIN</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>PETERS, ROBERT JAMES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HILL, JAMES FRENCH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITESIDES, GEORGE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIN, DAVE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DUNN, HARRY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IRWIN, JACQUI V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MENEFEE, CHRISTIAN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KRISHNAMOORTHI, S</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MIGUEZ, BLAKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STRICKLAND, MARILYN</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THANEDAR, SHRI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STEINMANN, JESSICA HART</x:t>
+  </x:si>
+  <x:si>
     <x:t>GOBER, CHRIS</x:t>
   </x:si>
   <x:si>
-    <x:t>10</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SELL, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19</x:t>
+    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEAN, MELISSA LUBURICH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEKARSKY, STELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00894428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MCKINNEY, AMANDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WARNER, MARK ROBERT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PATRONIS, JIMMY JR.</x:t>
   </x:si>
   <x:si>
     <x:t>NEHLS, TREVER</x:t>
   </x:si>
   <x:si>
-    <x:t>22</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DE LA CRUZ, CARLOS JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>35</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, AMANDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00848440</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PROTECT PROGRESS</x:t>
+    <x:t>TIMMONS, WILLIAM R IV</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROUNDS, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIEU, TED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLARK, JASMINE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MORRIS, NATE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LETLOW, JULIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUIZENGA, WILLIAM P</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEGICH, NICHOLAS III</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAGEMAN, HARRIET</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELBENE, SUZAN K</x:t>
   </x:si>
   <x:si>
     <x:t>STANTON, GREG</x:t>
   </x:si>
   <x:si>
     <x:t>AZ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAIRD, JAMES R DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TIMMONS, WILLIAM R IV</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCHRIER, KIM DR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>08</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00915181</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FELLOWSHIP PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GRAHAM, LINDSEY O.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROUNDS, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, FELIX BARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>COLLINS, MICHAEL A JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BARR, GARLAND ANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MORRIS, NATE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIGUEZ, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LETLOW, JULIA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RICKETTS, PETE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERN, KEVIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PAXTON, WARREN KENNETH JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WARNER, MARK ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAGEMAN, HARRIET</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00835959</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIRSHAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PETERS, ROBERT JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>OPPOSE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FORD, LA SHAWN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRATTON, JULIANA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FULLER, CLAY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, BLAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HILL, JAMES FRENCH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MOORE, TIM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PATRONIS, JIMMY JR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, RANDY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JAMES MORRIS</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GAINES, HOUSTON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SMITH, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BONCK, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEINMANN, JESSICA HART</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TORRES, RITCHIE JOHN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SCOTT, DAVID ALBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>13</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUDZINSKI, NIKKI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENENDEZ, ROBERT</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SIMON, LATEEFAH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LOFGREN, ZOE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WHITESIDES, GEORGE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>27</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LIEU, TED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MIN, DAVE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>47</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DUNN, HARRY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MD</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BAREEBE, QUINCY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELANEY, APRIL MCCLAIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GREEN, ALEXANDER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCGUIRE, MIKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IRWIN, JACQUI V</x:t>
-  </x:si>
-  <x:si>
-    <x:t>26</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SOLIS, HILDA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CORREA, LOU</x:t>
-  </x:si>
-  <x:si>
-    <x:t>46</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CLARK, JASMINE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEAN, MELISSA LUBURICH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BOAFO, ADRIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MENEFEE, CHRISTIAN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALKINSHAW, JAMES</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEKARSKY, STELLA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KELLY, ROBIN</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>KRISHNAMOORTHI, S</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00894428</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FIRST PRINCIPLES DIGITAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROGERS, MICHAEL J</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CARL, JERRY LEE, JR</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AUCHINCLOSS, JAKE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HUIZENGA, WILLIAM P</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DELBENE, SUZAN K</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STRICKLAND, MARILYN</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BEGICH, NICHOLAS III</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FRANKEL, LOIS J.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KINGSTON, JACK REP.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>THANEDAR, SHRI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GOODLANDER, MAGGIE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCKINNEY, DONAVAN</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -948,7 +948,7 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F2" s="1">
-        <x:v>461943</x:v>
+        <x:v>10015605</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
         <x:v>12</x:v>
@@ -956,91 +956,91 @@
     </x:row>
     <x:row r="3" spans="1:7">
       <x:c r="A3" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C3" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D3" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="1">
-        <x:v>91656</x:v>
+        <x:v>461942</x:v>
       </x:c>
       <x:c r="G3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
       <x:c r="A4" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D4" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>426280</x:v>
+        <x:v>426281</x:v>
       </x:c>
       <x:c r="G4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
       <x:c r="A5" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D5" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="F5" s="1">
-        <x:v>141263</x:v>
+        <x:v>262965</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
       <x:c r="A6" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D6" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="1">
-        <x:v>616386</x:v>
+        <x:v>47162</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
         <x:v>12</x:v>
@@ -1048,160 +1048,160 @@
     </x:row>
     <x:row r="7" spans="1:7">
       <x:c r="A7" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F7" s="1">
-        <x:v>506917</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:7">
       <x:c r="A8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F8" s="1">
-        <x:v>157560</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:7">
       <x:c r="A9" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="1">
-        <x:v>513868</x:v>
+        <x:v>500000</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:7">
       <x:c r="A10" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F10" s="1">
-        <x:v>487317</x:v>
+        <x:v>547042</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:7">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="1">
-        <x:v>105040</x:v>
+        <x:v>461943</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:7">
       <x:c r="A12" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="1">
-        <x:v>550000</x:v>
+        <x:v>426280</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:7">
       <x:c r="A13" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F13" s="1">
-        <x:v>411748</x:v>
+        <x:v>268690</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
         <x:v>12</x:v>
@@ -1209,114 +1209,114 @@
     </x:row>
     <x:row r="14" spans="1:7">
       <x:c r="A14" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F14" s="1">
-        <x:v>12203100</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:7">
       <x:c r="A15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F15" s="1">
         <x:v>350000</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:7">
       <x:c r="A16" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F16" s="1">
-        <x:v>350000</x:v>
+        <x:v>628597</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7">
       <x:c r="A17" s="1" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>44</x:v>
-      </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="1">
-        <x:v>628597</x:v>
+        <x:v>2250000</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7">
       <x:c r="A18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F18" s="1">
-        <x:v>221403</x:v>
+        <x:v>2479136</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
         <x:v>12</x:v>
@@ -1324,68 +1324,68 @@
     </x:row>
     <x:row r="19" spans="1:7">
       <x:c r="A19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>37</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
       <x:c r="F19" s="1">
-        <x:v>250000</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:7">
       <x:c r="A20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F20" s="1">
-        <x:v>350000</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:7">
       <x:c r="A21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F21" s="1">
-        <x:v>350000</x:v>
+        <x:v>56045</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>12</x:v>
@@ -1393,919 +1393,919 @@
     </x:row>
     <x:row r="22" spans="1:7">
       <x:c r="A22" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F22" s="1">
-        <x:v>735613</x:v>
+        <x:v>83860</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:7">
       <x:c r="A23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F23" s="1">
-        <x:v>300000</x:v>
+        <x:v>109274</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:7">
       <x:c r="A24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F24" s="1">
-        <x:v>2250000</x:v>
+        <x:v>5259858</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:7">
       <x:c r="A25" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F25" s="1">
-        <x:v>150000</x:v>
+        <x:v>1012792</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:7">
       <x:c r="A26" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F26" s="1">
-        <x:v>515838</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:7">
       <x:c r="A27" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F27" s="1">
-        <x:v>817066</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:7">
       <x:c r="A28" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F28" s="1">
-        <x:v>2479136</x:v>
+        <x:v>513868</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:7">
       <x:c r="A29" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F29" s="1">
-        <x:v>10015605</x:v>
+        <x:v>735613</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:7">
       <x:c r="A30" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F30" s="1">
-        <x:v>455146</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:7">
       <x:c r="A31" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F31" s="1">
-        <x:v>7170138</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:7">
       <x:c r="A32" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F32" s="1">
         <x:v>400022</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:7">
       <x:c r="A33" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F33" s="1">
-        <x:v>418058</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:7">
       <x:c r="A34" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F34" s="1">
-        <x:v>80948</x:v>
+        <x:v>1673736</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:7">
       <x:c r="A35" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F35" s="1">
-        <x:v>558813</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:7">
       <x:c r="A36" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D36" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E36" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F36" s="1">
-        <x:v>1673736</x:v>
+        <x:v>12254527</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:7">
       <x:c r="A37" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C37" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D37" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E37" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F37" s="1">
-        <x:v>430866</x:v>
+        <x:v>1419040</x:v>
       </x:c>
       <x:c r="G37" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:7">
       <x:c r="A38" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D38" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F38" s="1">
-        <x:v>708828</x:v>
+        <x:v>98455</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:7">
       <x:c r="A39" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C39" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D39" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E39" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F39" s="1">
-        <x:v>282975</x:v>
+        <x:v>382680</x:v>
       </x:c>
       <x:c r="G39" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:7">
       <x:c r="A40" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D40" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E40" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F40" s="1">
-        <x:v>348433</x:v>
+        <x:v>107387</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:7">
       <x:c r="A41" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C41" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D41" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E41" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F41" s="1">
-        <x:v>771658</x:v>
+        <x:v>455146</x:v>
       </x:c>
       <x:c r="G41" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:7">
       <x:c r="A42" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D42" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F42" s="1">
-        <x:v>461942</x:v>
+        <x:v>400022</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:7">
       <x:c r="A43" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C43" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D43" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E43" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F43" s="1">
-        <x:v>91656</x:v>
+        <x:v>80948</x:v>
       </x:c>
       <x:c r="G43" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:7">
       <x:c r="A44" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D44" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E44" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F44" s="1">
-        <x:v>426281</x:v>
+        <x:v>282975</x:v>
       </x:c>
       <x:c r="G44" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:7">
       <x:c r="A45" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C45" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D45" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E45" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F45" s="1">
-        <x:v>141263</x:v>
+        <x:v>12203100</x:v>
       </x:c>
       <x:c r="G45" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:7">
       <x:c r="A46" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C46" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D46" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E46" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F46" s="1">
-        <x:v>615886</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G46" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:7">
       <x:c r="A47" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C47" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D47" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E47" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F47" s="1">
-        <x:v>513868</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G47" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:7">
       <x:c r="A48" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C48" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D48" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E48" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F48" s="1">
-        <x:v>487316</x:v>
+        <x:v>111599</x:v>
       </x:c>
       <x:c r="G48" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:7">
       <x:c r="A49" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C49" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D49" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E49" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F49" s="1">
-        <x:v>411748</x:v>
+        <x:v>380377</x:v>
       </x:c>
       <x:c r="G49" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:7">
       <x:c r="A50" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C50" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D50" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E50" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F50" s="1">
-        <x:v>12254527</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G50" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:7">
       <x:c r="A51" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C51" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D51" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E51" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F51" s="1">
-        <x:v>735613</x:v>
+        <x:v>7170138</x:v>
       </x:c>
       <x:c r="G51" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:7">
       <x:c r="A52" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C52" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D52" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E52" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F52" s="1">
-        <x:v>1419040</x:v>
+        <x:v>348433</x:v>
       </x:c>
       <x:c r="G52" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:7">
       <x:c r="A53" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C53" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="D53" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="E53" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="D53" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="E53" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="F53" s="1">
-        <x:v>56045</x:v>
+        <x:v>189528</x:v>
       </x:c>
       <x:c r="G53" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:7">
       <x:c r="A54" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C54" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D54" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D54" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
       <x:c r="E54" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F54" s="1">
-        <x:v>83860</x:v>
+        <x:v>151713</x:v>
       </x:c>
       <x:c r="G54" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:7">
       <x:c r="A55" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B55" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C55" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D55" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B55" s="1" t="s">
+      <x:c r="E55" s="1" t="s">
         <x:v>25</x:v>
       </x:c>
-      <x:c r="C55" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D55" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="E55" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="F55" s="1">
-        <x:v>262965</x:v>
+        <x:v>34890</x:v>
       </x:c>
       <x:c r="G55" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:7">
       <x:c r="A56" s="1" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B56" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C56" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D56" s="1" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B56" s="1" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="C56" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="D56" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="E56" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F56" s="1">
-        <x:v>111599</x:v>
+        <x:v>105040</x:v>
       </x:c>
       <x:c r="G56" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:7">
       <x:c r="A57" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C57" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D57" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E57" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F57" s="1">
-        <x:v>109274</x:v>
+        <x:v>550000</x:v>
       </x:c>
       <x:c r="G57" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:7">
       <x:c r="A58" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C58" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D58" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E58" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F58" s="1">
-        <x:v>487174</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G58" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:7">
       <x:c r="A59" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C59" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D59" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E59" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F59" s="1">
-        <x:v>106348</x:v>
+        <x:v>708828</x:v>
       </x:c>
       <x:c r="G59" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:7">
       <x:c r="A60" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C60" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D60" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E60" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F60" s="1">
-        <x:v>107940</x:v>
+        <x:v>516368</x:v>
       </x:c>
       <x:c r="G60" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:7">
       <x:c r="A61" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C61" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D61" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E61" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F61" s="1">
-        <x:v>172296</x:v>
+        <x:v>119844</x:v>
       </x:c>
       <x:c r="G61" s="1" t="s">
         <x:v>12</x:v>
@@ -2313,137 +2313,137 @@
     </x:row>
     <x:row r="62" spans="1:7">
       <x:c r="A62" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C62" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="D62" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E62" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F62" s="1">
-        <x:v>98455</x:v>
+        <x:v>285009</x:v>
       </x:c>
       <x:c r="G62" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:7">
       <x:c r="A63" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C63" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D63" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E63" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F63" s="1">
-        <x:v>516368</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G63" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:7">
       <x:c r="A64" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C64" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D64" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E64" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F64" s="1">
-        <x:v>47162</x:v>
+        <x:v>430866</x:v>
       </x:c>
       <x:c r="G64" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:7">
       <x:c r="A65" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C65" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D65" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E65" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F65" s="1">
-        <x:v>382680</x:v>
+        <x:v>708827</x:v>
       </x:c>
       <x:c r="G65" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:7">
       <x:c r="A66" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C66" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D66" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E66" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="F66" s="1">
-        <x:v>377124</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G66" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:7">
       <x:c r="A67" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C67" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D67" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E67" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F67" s="1">
-        <x:v>380377</x:v>
+        <x:v>817066</x:v>
       </x:c>
       <x:c r="G67" s="1" t="s">
         <x:v>12</x:v>
@@ -2451,459 +2451,459 @@
     </x:row>
     <x:row r="68" spans="1:7">
       <x:c r="A68" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C68" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D68" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E68" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F68" s="1">
-        <x:v>107387</x:v>
+        <x:v>418058</x:v>
       </x:c>
       <x:c r="G68" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:7">
       <x:c r="A69" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C69" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D69" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E69" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F69" s="1">
-        <x:v>4239904</x:v>
+        <x:v>487174</x:v>
       </x:c>
       <x:c r="G69" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:7">
       <x:c r="A70" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C70" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D70" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E70" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F70" s="1">
-        <x:v>557012</x:v>
+        <x:v>107940</x:v>
       </x:c>
       <x:c r="G70" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:7">
       <x:c r="A71" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C71" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D71" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E71" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F71" s="1">
-        <x:v>5259858</x:v>
+        <x:v>172296</x:v>
       </x:c>
       <x:c r="G71" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:7">
       <x:c r="A72" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C72" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D72" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E72" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F72" s="1">
-        <x:v>6471279</x:v>
+        <x:v>377124</x:v>
       </x:c>
       <x:c r="G72" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:7">
       <x:c r="A73" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C73" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="D73" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E73" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F73" s="1">
-        <x:v>1012792</x:v>
+        <x:v>6471279</x:v>
       </x:c>
       <x:c r="G73" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:7">
       <x:c r="A74" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C74" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D74" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E74" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F74" s="1">
-        <x:v>20483</x:v>
+        <x:v>30220</x:v>
       </x:c>
       <x:c r="G74" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:7">
       <x:c r="A75" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C75" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D75" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E75" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F75" s="1">
-        <x:v>119844</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G75" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:7">
       <x:c r="A76" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C76" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D76" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E76" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F76" s="1">
-        <x:v>285009</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G76" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:7">
       <x:c r="A77" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C77" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D77" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E77" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F77" s="1">
-        <x:v>30220</x:v>
+        <x:v>418060</x:v>
       </x:c>
       <x:c r="G77" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:7">
       <x:c r="A78" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C78" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D78" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E78" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F78" s="1">
-        <x:v>91847</x:v>
+        <x:v>103020</x:v>
       </x:c>
       <x:c r="G78" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:7">
       <x:c r="A79" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C79" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D79" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E79" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F79" s="1">
-        <x:v>300000</x:v>
+        <x:v>1762153</x:v>
       </x:c>
       <x:c r="G79" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:7">
       <x:c r="A80" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C80" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D80" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E80" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
       <x:c r="F80" s="1">
-        <x:v>550000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G80" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:7">
       <x:c r="A81" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C81" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D81" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E81" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F81" s="1">
-        <x:v>350000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="G81" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:7">
       <x:c r="A82" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C82" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D82" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E82" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F82" s="1">
-        <x:v>350000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G82" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:7">
       <x:c r="A83" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C83" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D83" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E83" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F83" s="1">
-        <x:v>628597</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G83" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:7">
       <x:c r="A84" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C84" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D84" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E84" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F84" s="1">
-        <x:v>221403</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G84" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:7">
       <x:c r="A85" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C85" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D85" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E85" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F85" s="1">
-        <x:v>250000</x:v>
+        <x:v>615886</x:v>
       </x:c>
       <x:c r="G85" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:7">
       <x:c r="A86" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C86" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D86" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E86" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F86" s="1">
-        <x:v>350000</x:v>
+        <x:v>557012</x:v>
       </x:c>
       <x:c r="G86" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:7">
       <x:c r="A87" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C87" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D87" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E87" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F87" s="1">
-        <x:v>350000</x:v>
+        <x:v>20483</x:v>
       </x:c>
       <x:c r="G87" s="1" t="s">
         <x:v>12</x:v>
@@ -2911,600 +2911,600 @@
     </x:row>
     <x:row r="88" spans="1:7">
       <x:c r="A88" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C88" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D88" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E88" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F88" s="1">
-        <x:v>300000</x:v>
+        <x:v>91847</x:v>
       </x:c>
       <x:c r="G88" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:7">
       <x:c r="A89" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C89" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D89" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E89" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F89" s="1">
-        <x:v>500000</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G89" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:7">
       <x:c r="A90" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C90" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D90" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E90" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F90" s="1">
-        <x:v>547042</x:v>
+        <x:v>771658</x:v>
       </x:c>
       <x:c r="G90" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
       <x:c r="A91" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C91" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D91" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E91" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F91" s="1">
-        <x:v>455146</x:v>
+        <x:v>91656</x:v>
       </x:c>
       <x:c r="G91" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:7">
       <x:c r="A92" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C92" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D92" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E92" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F92" s="1">
-        <x:v>300000</x:v>
+        <x:v>616386</x:v>
       </x:c>
       <x:c r="G92" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:7">
       <x:c r="A93" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C93" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D93" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E93" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F93" s="1">
-        <x:v>7170138</x:v>
+        <x:v>506917</x:v>
       </x:c>
       <x:c r="G93" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:7">
       <x:c r="A94" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C94" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D94" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E94" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="F94" s="1">
-        <x:v>189528</x:v>
+        <x:v>300000</x:v>
       </x:c>
       <x:c r="G94" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:7">
       <x:c r="A95" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C95" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="D95" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E95" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F95" s="1">
-        <x:v>511996</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="G95" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:7">
       <x:c r="A96" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C96" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="D96" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E96" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F96" s="1">
-        <x:v>300000</x:v>
+        <x:v>558813</x:v>
       </x:c>
       <x:c r="G96" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:7">
       <x:c r="A97" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C97" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D97" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E97" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F97" s="1">
-        <x:v>400022</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G97" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:7">
       <x:c r="A98" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C98" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D98" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E98" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F98" s="1">
-        <x:v>113120</x:v>
+        <x:v>487316</x:v>
       </x:c>
       <x:c r="G98" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:7">
       <x:c r="A99" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C99" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D99" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E99" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F99" s="1">
-        <x:v>103020</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G99" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:7">
       <x:c r="A100" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C100" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D100" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E100" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F100" s="1">
-        <x:v>508142</x:v>
+        <x:v>106348</x:v>
       </x:c>
       <x:c r="G100" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:7">
       <x:c r="A101" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C101" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="D101" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E101" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F101" s="1">
-        <x:v>151713</x:v>
+        <x:v>4239904</x:v>
       </x:c>
       <x:c r="G101" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:7">
       <x:c r="A102" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C102" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D102" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E102" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F102" s="1">
-        <x:v>430866</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G102" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:7">
       <x:c r="A103" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C103" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D103" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E103" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F103" s="1">
-        <x:v>1762153</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G103" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:7">
       <x:c r="A104" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C104" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="D104" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E104" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="F104" s="1">
-        <x:v>34890</x:v>
+        <x:v>511996</x:v>
       </x:c>
       <x:c r="G104" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:7">
       <x:c r="A105" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C105" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="D105" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E105" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>418060</x:v>
+        <x:v>508142</x:v>
       </x:c>
       <x:c r="G105" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
       <x:c r="A106" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C106" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="D106" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E106" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>80948</x:v>
+        <x:v>141263</x:v>
       </x:c>
       <x:c r="G106" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
       <x:c r="A107" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C107" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D107" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E107" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="F107" s="1">
-        <x:v>150000</x:v>
+        <x:v>487317</x:v>
       </x:c>
       <x:c r="G107" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="108" spans="1:7">
       <x:c r="A108" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B108" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C108" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="D108" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E108" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F108" s="1">
-        <x:v>430866</x:v>
+        <x:v>411748</x:v>
       </x:c>
       <x:c r="G108" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="109" spans="1:7">
       <x:c r="A109" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B109" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C109" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D109" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E109" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="F109" s="1">
-        <x:v>708827</x:v>
+        <x:v>515838</x:v>
       </x:c>
       <x:c r="G109" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="110" spans="1:7">
       <x:c r="A110" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B110" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C110" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="D110" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E110" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F110" s="1">
-        <x:v>268690</x:v>
+        <x:v>113120</x:v>
       </x:c>
       <x:c r="G110" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="111" spans="1:7">
       <x:c r="A111" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B111" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C111" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="D111" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E111" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="F111" s="1">
-        <x:v>282975</x:v>
+        <x:v>157560</x:v>
       </x:c>
       <x:c r="G111" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
       <x:c r="A112" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B112" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C112" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="D112" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E112" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F112" s="1">
-        <x:v>348433</x:v>
+        <x:v>221403</x:v>
       </x:c>
       <x:c r="G112" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="113" spans="1:7">
       <x:c r="A113" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="B113" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C113" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="D113" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="E113" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="F113" s="1">
-        <x:v>771658</x:v>
+        <x:v>350000</x:v>
       </x:c>
       <x:c r="G113" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3553,1277 +3553,1277 @@
     </x:row>
     <x:row r="2" spans="1:5">
       <x:c r="A2" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D2" s="1">
         <x:v>508142</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:5">
       <x:c r="A3" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C3" s="1" t="s">
         <x:v>37</x:v>
-      </x:c>
-      <x:c r="C3" s="1" t="s">
-        <x:v>41</x:v>
       </x:c>
       <x:c r="D3" s="1">
         <x:v>25157627</x:v>
       </x:c>
       <x:c r="E3" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:5">
       <x:c r="A4" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D4" s="1">
         <x:v>547042</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:5">
       <x:c r="A5" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D5" s="1">
         <x:v>836118</x:v>
       </x:c>
       <x:c r="E5" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:5">
       <x:c r="A6" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D6" s="1">
         <x:v>157560</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:5">
       <x:c r="A7" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>382680</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:5">
       <x:c r="A8" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>111599</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:5">
       <x:c r="A9" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>109274</x:v>
       </x:c>
       <x:c r="E9